--- a/data/医小星教学大纲.xlsx
+++ b/data/医小星教学大纲.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="376">
   <si>
     <t>疾病</t>
   </si>
@@ -585,6 +585,576 @@
   </si>
   <si>
     <t>1. **肺癌驱动基因**：讲解EGFR、ALK等检测的必要性。\n2. **骨转移的局部治疗**：提问放疗、双膦酸盐的应用。\n3. **支持治疗**：提问止痛、营养、心理支持。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“脑中风的警报”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（突发偏瘫、失语、高血压史）。提问：“从患者的描述和查体中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“突发神经系统功能障碍，应首先区分缺血还是出血？如何快速鉴别？”\n3. **紧急处理**：提问：“在等待影像学结果时，应采取哪些基本措施？”\n4. **辅助检查选择**：提问：“首选什么检查？为什么？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（老年、高血压）。\n2. **脑卒中分类**：提问缺血性与出血性卒中的区别。\n3. **危险因素**：提问常见可干预危险因素。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读影像结果**：提问：“头颅CT排除出血，MRI示梗死，下一步治疗关键是什么？”\n2. **溶栓评估**：提问：“溶栓的适应证和禁忌证？如何计算时间窗？”\n3. **与家属沟通**：引导学生向家属解释溶栓的必要性和风险。\n4. **替代治疗**：提问：“错过溶栓窗后应如何治疗？”\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **溶栓药物**：讲解rt-PA的作用机制。\n2. **抗血小板药物**：提问阿司匹林、氯吡格雷的应用。\n3. **抗凝治疗**：提问在心源性栓塞中的应用。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **康复时机**：提问：“何时开始康复训练？主要内容有哪些？”\n2. **二级预防**：提问：“如何通过药物和生活方式预防复发？”\n3. **血压管理**：提问：“卒中后血压控制目标是多少？”\n4. **患者教育**：引导学生向患者解释长期用药的必要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **康复分期**：讲解急性期、恢复期、后遗症期的康复重点。\n2. **抗血小板二级预防**：提问阿司匹林与他汀的联合应用。\n3. **生活方式干预**：提问饮食、运动、戒烟限酒。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院前评估**：提问：“患者出院时需达到什么标准？”\n2. **出院指导**：提问：“用药、复查、注意事项有哪些？”\n3. **复发预警**：提问：“出现哪些症状需立即就医？”\n4. **患者教育**：引导学生强调定期随访的重要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **随访计划**：讲解复查频率及项目。\n2. **二级预防指南**：提问国内外指南推荐。\n3. **家庭护理**：提问家属如何协助康复。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“半身风云”</t>
+  </si>
+  <si>
+    <t>“惊厥之舞”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（突发意识丧失、四肢抽搐、口吐白沫）。提问：“从患者的描述和目击者描述中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“抽搐发作应与哪些疾病鉴别（晕厥、癔症、低血糖）？”\n3. **紧急处理**：提问：“发作时现场应如何正确处理？”\n4. **辅助检查**：提问：“应首选什么检查明确诊断？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（青年男性、无诱因）。\n2. **癫痫定义与分类**：提问全面性发作与部分性发作的区别。\n3. **病因学**：提问特发性、症状性癫痫的常见原因。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读脑电图**：提问：“脑电图示棘慢波，有何临床意义？”\n2. **诊断确立**：提问：“根据病史和脑电图，可以确定诊断吗？”\n3. **治疗决策**：提问：“首次发作患者是否需要立即用药？为什么？”\n4. **与患者沟通**：引导学生向患者解释病情及治疗选择。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **抗癫痫药物分类**：讲解传统与新型AED。\n2. **药物选择原则**：提问根据发作类型选药。\n3. **治疗目标**：提问控制发作、减少副作用。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **药物副作用**：提问：“丙戊酸钠引起嗜睡，如何处理？需要监测哪些指标？”\n2. **血药浓度**：提问：“为什么要监测血药浓度？目标范围是多少？”\n3. **剂量调整**：提问：“如何根据副作用和浓度调整剂量？”\n4. **患者教育**：引导学生告知患者坚持服药的重要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **常见副作用**：讲解肝损、血小板减少、嗜睡等。\n2. **药物相互作用**：提问其他药物对AED的影响。\n3. **血药浓度监测**：提问采血时机、临床意义。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“出院后如何用药？多久复查？”\n2. **生活注意事项**：提问：“能否开车、游泳、熬夜？”\n3. **复发风险**：提问：“停药后复发率？停药原则？”\n4. **患者教育**：引导学生回答患者关心的问题。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **停药原则**：讲解完全控制2-5年后逐渐减停。\n2. **复发因素**：提问年龄、病因、发作类型的影响。\n3. **社会心理支持**：提问如何帮助患者回归正常生活。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“隐形的枷锁”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（情绪低落、兴趣减退、失眠、自杀念头）。提问：“从患者的描述中，你捕捉到了哪些关键信息呢？”\n2. **风险评估**：提问：“患者有自杀念头，应如何评估紧急程度？”\n3. **鉴别诊断**：提问：“需与哪些疾病鉴别（如甲状腺功能减退、焦虑症）？”\n4. **初步检查**：提问：“应做哪些检查排除躯体疾病？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（中年女性、近期压力）。\n2. **抑郁症流行病学**：提问患病率、性别差异。\n3. **病因学**：提问生物、心理、社会因素。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读量表**：提问：“PHQ-9 18分提示什么？”\n2. **治疗选择**：提问：“药物治疗 vs 心理治疗，如何选择？”\n3. **药物介绍**：提问：“SSRI类药物的作用机制、常用药物？”\n4. **与患者沟通**：引导学生解释药物治疗的必要性，打消顾虑。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **抗抑郁药分类**：讲解SSRI、SNRI、NaSSA等。\n2. **心理治疗**：提问CBT、IPT的适应证。\n3. **药物起效时间**：提问2-4周显效的原因。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **副作用处理**：提问：“恶心如何处理？能否自行停药？”\n2. **调整方案**：提问：“效果不佳时如何调整剂量或换药？”\n3. **依从性教育**：引导学生强调坚持服药的重要性。\n4. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **常见副作用**：讲解SSRI的消化道症状、性功能障碍。\n2. **药物相互作用**：提问与其他药物的影响。\n3. **换药原则**：提问逐渐加量、交叉换药。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院标准**：提问：“患者症状好转，如何判断是否适合出院？”\n2. **维持治疗**：提问：“为何需要继续服药？要服多久？”\n3. **复发预防**：提问：“如何识别复发先兆？”\n4. **患者教育**：引导学生回答患者及家属的问题。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **维持治疗**：讲解急性期、巩固期、维持期。\n2. **复发因素**：提问残留症状、社会支持的影响。\n3. **社会康复**：提问工作、生活指导。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“心弦紧绷”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（胸骨后压榨性疼痛、向左肩放射、劳累诱发、硝酸甘油缓解）。提问：“从患者的描述中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“胸痛的鉴别诊断有哪些？如何区分心绞痛与心梗？”\n3. **危险因素**：提问：“患者有哪些冠心病危险因素？”\n4. **初步检查**：提问：“应首选哪些检查？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（中年男性、高血压、高血脂、工作压力大）。\n2. **冠心病病理**：提问动脉粥样硬化斑块的形成机制。\n3. **心绞痛分级**：提问加拿大心血管学会（CCS）分级。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读检查结果**：提问：“心电图ST段压低，心肌酶正常，说明什么？”\n2. **治疗选择**：提问：“药物保守治疗 vs 介入治疗，如何选择？”\n3. **手术风险**：提问：“冠脉造影和支架植入的风险有哪些？”\n4. **与患者沟通**：引导学生向家属解释手术必要性，打消顾虑。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **冠脉解剖**：讲解左前降支、回旋支、右冠状动脉的供血范围。\n2. **介入治疗**：提问球囊扩张、支架植入的过程。\n3. **抗血小板药物**：提问阿司匹林、氯吡格雷的作用机制。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **术后评估**：提问：“术后胸痛消失，说明手术成功，下一步治疗重点是什么？”\n2. **双抗治疗**：提问：“为什么需要双抗？要服多久？”\n3. **副作用监测**：提问：“阿司匹林引起胃肠道出血怎么办？”\n4. **患者教育**：引导学生向患者解释坚持服药的重要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **双抗疗程**：讲解根据支架类型（DES/BMS）决定DAPT时长。\n2. **他汀类药物的多效性**：提问降脂外的作用。\n3. **再狭窄机制**：提问内膜增生、支架内血栓。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院前评估**：提问：“患者出院前需达到哪些标准？”\n2. **出院指导**：提问：“用药、饮食、运动、复查注意事项？”\n3. **复发预警**：提问：“出现哪些症状需立即就医？”\n4. **患者教育**：引导学生强调健康生活方式的重要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **二级预防指南**：讲解ABCDE方案（阿司匹林、血压控制、降脂、戒烟、饮食运动等）。\n2. **心脏康复**：提问康复分期及内容。\n3. **心理支持**：提问如何帮助患者克服焦虑。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“心跳乱了”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（突感心悸、胸闷、气短、头晕）。提问：“从患者的描述和查体中，你捕捉到了哪些关键信息呢？”\n2. **体格检查**：提问：“心律绝对不齐、第一心音强弱不等、脉搏短绌，提示什么？”\n3. **辅助检查**：提问：“首选什么检查确诊？”\n4. **紧急处理**：提问：“快速房颤伴血流动力学不稳定应如何处理？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（老年、高血压）。\n2. **房颤分类**：提问阵发性、持续性、永久性房颤的区别。\n3. **房颤机制**：讲解心房电重构和结构重构。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读评分**：提问：“CHA2DS2-VASc评分4分，HAS-BLED评分2分，说明了什么？”\n2. **抗凝选择**：提问：“华法林 vs NOAC，如何选择？”\n3. **抗凝监测**：提问：“华法林为什么需要监测INR？目标范围是多少？”\n4. **与患者沟通**：引导学生向患者解释抗凝的必要性和风险。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **抗凝药物**：讲解华法林及NOAC的作用机制。\n2. **抗凝管理**：提问INR监测频率、影响因素。\n3. **出血处理**：提问抗凝相关出血的应对策略。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **转复后管理**：提问：“转复窦律后，还需要抗凝吗？”\n2. **长期抗凝**：提问：“房颤患者抗凝治疗的疗程？”\n3. **药物副作用**：提问：“服用华法林期间出现瘀斑怎么办？”\n4. **患者教育**：引导学生告知患者坚持服药和定期监测的重要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **抗凝疗程**：讲解根据卒中风险评估决定长期抗凝。\n2. **药物相互作用**：提问影响华法林药效的食物和药物。\n3. **漏服处理**：提问漏服抗凝药的应对措施。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“出院后如何监测INR？多久一次？”\n2. **生活方式**：提问：“饮食上有哪些注意事项（避免大量富含VitK的食物）？”\n3. **复发预防**：提问：“如何预防房颤复发（控制血压、心率、避免诱因）？”\n4. **患者教育**：引导学生回答患者关心的问题。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **抗凝管理**：讲解华法林剂量调整原则。\n2. **房颤射频消融**：提问适应证及效果。\n3. **左心耳封堵**：提问适用于抗凝禁忌患者。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“泵的挣扎”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（突发呼吸困难、端坐呼吸、咳粉红色泡沫样痰、高血压）。提问：“从患者的描述和查体中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“急性呼吸困难应与哪些疾病鉴别（COPD、哮喘、肺栓塞）？”\n3. **紧急处理**：提问：“急性心衰的抢救流程（吸氧、利尿、扩血管、强心）？”\n4. **药物选择**：提问：“为什么首选呋塞米？硝酸甘油的作用？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（老年、冠心病史、感染诱因）。\n2. **心衰定义与分类**：提问左心衰、右心衰、全心衰的区别。\n3. **Frank-Starling机制**：讲解心衰时的代偿与失代偿。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读检查结果**：提问：“心脏超声示LVEF35%，BNP 5000pg/ml，说明什么？”\n2. **心衰分期**：提问：“患者处于哪一期（A、B、C、D）？”\n3. **病因治疗**：提问：“缺血性心肌病如何改善心肌血供？”\n4. **与患者沟通**：引导学生向患者及家属解释病情及预后。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **心衰药物分类**：讲解利尿剂、ACEI/ARB、β阻滞剂、洋地黄的作用。\n2. **心衰的非药物治疗**：提问CRT、ICD的适应证。\n3. **容量管理**：提问出入量、体重监测的意义。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **长期治疗**：提问：“心衰患者需要终身服药吗？”\n2. **药物副作用**：提问：“ACEI引起干咳怎么办？β阻滞剂引起心动过缓怎么办？”\n3. **依从性教育**：引导学生告知患者坚持服药的重要性。\n4. **康复指导**：提问：“心衰患者如何适度运动？”\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **药物作用机制**：讲解RAAS系统与交感神经在心衰中的作用。\n2. **药物相互作用**：提问联合用药注意事项。\n3. **心衰加重诱因**：提问感染、心律失常、劳累、钠水潴留。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“限盐多少克？限水多少毫升？”\n2. **自我监测**：提问：“每天称体重、记录尿量，出现什么情况需就医？”\n3. **随访计划**：提问：“多久复查一次？复查哪些项目？”\n4. **患者教育**：引导学生回答患者关心的问题。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **心衰管理指南**：讲解国内外指南推荐。\n2. **姑息治疗**：提问终末期心衰的处理。\n3. **心理支持**：提问如何帮助患者克服焦虑。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“喘息的风箱”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（突发呼吸困难、喘息、胸闷、端坐呼吸）。提问：“从患者的描述和查体中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“喘息、呼吸困难需与哪些疾病鉴别（心源性哮喘、COPD、气道异物）？”\n3. **紧急处理**：提问：“哮喘急性发作时如何迅速缓解症状？”\n4. **辅助检查**：提问：“应首选哪些检查？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（青年男性、过敏性鼻炎史）。\n2. **哮喘定义**：提问支气管哮喘的病理生理特点。\n3. **触发因素**：提问常见过敏原和刺激物。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读肺功能**：提问：“FEV1/FVC&lt;70%，支气管舒张试验阳性，说明了什么？”\n2. **控制水平评估**：提问：“如何评估哮喘控制水平（GINA指南）？”\n3. **长期治疗**：提问：“哮喘长期控制治疗的首选药物是什么？为什么需要吸入激素？”\n4. **与患者沟通**：引导学生向患者解释长期治疗的必要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **哮喘阶梯治疗**：讲解GINA阶梯式治疗方案。\n2. **吸入装置**：提问压力定量气雾剂、干粉吸入剂的正确使用方法。\n3. **峰流速监测**：提问监测频率及记录方法。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **副作用管理**：提问：“吸入糖皮质激素的常见副作用及如何预防？”\n2. **依从性教育**：提问：“患者担心激素副作用而自行停药怎么办？”\n3. **急性发作预警**：提问：“出现哪些症状提示即将急性发作？”\n4. **患者教育**：引导学生向患者强调规律用药的重要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **药物相互作用**：提问β2受体激动剂与激素的协同作用。\n2. **难治性哮喘**：提问处理原则。\n3. **生物制剂**：介绍抗IgE抗体、抗IL-5抗体。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“出院后如何规律用药？峰流速监测频率？”\n2. **避免诱因**：提问：“如何避免尘螨、花粉等过敏原？”\n3. **行动计划**：提问：“如何制定哮喘行动计划（绿区、黄区、红区）？”\n4. **患者教育**：引导学生回答患者关于运动、饮食、宠物等问题。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **哮喘与妊娠**：提问妊娠期哮喘管理。\n2. **哮喘与运动**：提问运动性哮喘的预防。\n3. **心理支持**：提问如何帮助患者克服焦虑。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“被困的气泡”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（运动后突发胸痛、呼吸困难）。提问：“从患者的描述和查体中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“突发胸痛、呼吸困难需与哪些疾病鉴别（心梗、肺栓塞、心包炎）？”\n3. **体格检查**：提问：“患侧呼吸音消失、叩诊鼓音，提示什么？”\n4. **辅助检查**：提问：“首选什么检查确诊？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（青年、瘦高体型、运动）。\n2. **气胸分类**：提问自发性、外伤性、医源性气胸的区别。\n3. **病因学**：提问肺大疱破裂的机制。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读影像**：提问：“X线示肺压缩40%，说明什么？”\n2. **治疗选择**：提问：“保守观察 vs 闭式引流，如何选择？”\n3. **操作解释**：提问：“胸腔闭式引流的原理、步骤、风险？”\n4. **与患者沟通**：引导学生向患者解释治疗必要性，打消顾虑。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **胸腔闭式引流装置**：讲解水封瓶的结构及工作原理。\n2. **引流护理**：提问保持通畅、防止脱出、观察水柱波动。\n3. **并发症**：提问感染、出血、复张性肺水肿。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **术后观察**：提问：“如何判断漏气已停止？肺是否复张？”\n2. **拔管时机**：提问：“拔管前需满足哪些条件？”\n3. **拔管操作**：提问：“拔管时患者应如何配合？拔管后如何处理？”\n4. **患者教育**：引导学生向患者说明注意事项。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **漏气分级**：讲解持续性漏气的原因及处理。\n2. **复张性肺水肿**：提问快速复张导致的并发症及预防。\n3. **拔管后观察**：提问观察呼吸困难、皮下气肿等。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“出院后多久可以恢复运动？哪些运动不能做？”\n2. **复发预防**：提问：“如何降低复发风险（戒烟、避免气压剧变）？”\n3. **生活建议**：提问：“能否坐飞机？多久可以？”\n4. **患者教育**：引导学生回答患者关心的问题。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **气胸复发率**：讲解首次发作后复发概率及影响因素。\n2. **手术治疗**：提问肺大疱切除术、胸膜固定术的适应证。\n3. **航空医学**：提问气胸患者乘机指南。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“沉默的阴影”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（刺激性干咳、痰中带血、消瘦、长期吸烟）。提问：“从患者的描述中，你捕捉到了哪些关键信息呢？”\n2. **危险因素**：提问：“吸烟与肺癌的关系？包年如何计算？”\n3. **鉴别诊断**：提问：“咳嗽、咯血需与哪些疾病鉴别（肺结核、支气管扩张、肺炎）？”\n4. **初步检查**：提问：“应首选哪些检查？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（老年、男性、长期吸烟）。\n2. **肺癌分类**：提问非小细胞肺癌与小细胞肺癌的区别。\n3. **流行病学**：提问肺癌的发病率、死亡率。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读检查结果**：提问：“CT示右肺上叶占位、纵隔淋巴结肿大，提示什么？活检病理为鳞癌，有何临床意义？”\n2. **分期评估**：提问：“为什么需要PET-CT？N2是什么意思？”\n3. **治疗选择**：提问：“根据分期，有哪些治疗选择？”\n4. **与患者沟通**：引导学生向患者解释病情，注意保护性医疗。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **TNM分期系统**：讲解T、N、M的含义及分期组合。\n2. **肺癌标志物**：提问CYFRA21-1、SCC、CEA的意义。\n3. **治疗原则**：提问不同期别的治疗策略（手术、化疗、放疗、靶向）。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **新辅助化疗**：提问：“新辅助化疗的优缺点？哪些患者适合？”\n2. **同步放化疗**：提问：“Ⅲ期不可切除肺癌的标准治疗是什么？”\n3. **决策支持**：提问：“如何帮助家属在多种治疗方案中选择？”\n4. **与家属沟通**：引导学生解释利弊，尊重患者意愿。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **化疗方案**：介绍常用方案（紫杉醇+卡铂、吉西他滨+顺铂等）。\n2. **放疗技术**：提问IMRT、SBRT的优势。\n3. **靶向治疗**：提问EGFR、ALK等驱动基因检测的必要性。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **术后管理**：提问：“术后需注意哪些问题？如何促进康复？”\n2. **随访计划**：提问：“肺癌术后应如何随访（频率、检查项目）？”\n3. **二级预防**：提问：“如何预防复发（戒烟、健康生活方式）？”\n4. **患者教育**：引导学生回答患者关于戒烟、饮食、运动的问题。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **复发监测**：讲解影像学、肿瘤标志物的应用。\n2. **支持治疗**：提问疼痛管理、营养支持、心理支持。\n3. **临终关怀**：提问终末期患者的安宁疗护。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“胃里的火山”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（饥饿痛、夜间痛、进食缓解）。提问：“从患者的描述中，你捕捉到了哪些关键信息呢？”\n2. **分析可能病因**：结合背景信息（工作压力、饮食不规律），提问：“结合患者的背景，你觉得这些表现可能是什么原因导致的？”\n3. **鉴别诊断**：提问：“上腹痛有哪些常见原因？如何鉴别溃疡与其他疾病？”\n4. **推荐辅助检查**：提问：“应首选哪些检查确诊？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（中年男性、工作压力、饮食不规律）。\n2. **消化性溃疡病因**：提问消化性溃疡的常见病因（Hp感染、NSAIDs、应激等）。\n3. **发病机制**：提问胃酸、胃蛋白酶在溃疡形成中的作用。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读检查结果**：提问：“胃镜示A1期溃疡，Hp阳性，说明了什么？”\n2. **分析治疗选择**：提问：“为什么需要抗Hp治疗？根除Hp的意义？”\n3. **治疗方案**：提问：“根除Hp的常用方案有哪些？注意事项？”\n4. **与患者沟通**：引导学生解释住院治疗的必要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **幽门螺杆菌**：讲解Hp的传播、致病机制。\n2. **抗Hp药物**：介绍抗生素、PPI、铋剂的作用。\n3. **根除失败原因**：提问耐药、依从性差等。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **分析病情**：提问：“患者症状消失但溃疡未完全愈合，可能的原因？”\n2. **难治性溃疡处理**：提问：“需要做哪些检查明确病因（复查胃镜、排除胃泌素瘤）？”\n3. **调整方案**：提问：“如何调整治疗（延长疗程、换用更强效PPI）？”\n4. **患者教育**：引导学生解释持续治疗的必要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **难治性溃疡定义**：提问规范治疗8周未愈合。\n2. **病因分析**：提问Hp耐药、隐匿性NSAID使用、胃泌素瘤等。\n3. **鉴别诊断**：提问胃癌、克罗恩病等。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **评估疗效**：提问：“溃疡完全愈合，Hp转阴，说明治疗成功。出院后如何管理？”\n2. **出院指导**：提问：“用药、饮食、复查注意事项？”\n3. **预防复发**：提问：“如何预防溃疡复发（避免NSAIDs、规律饮食、复查Hp）？”\n4. **患者教育**：引导学生回答患者关于生活方式的疑问。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **溃疡复发机制**：讲解Hp再感染、长期服用NSAIDs等。\n2. **二级预防**：提问定期复查胃镜、根除Hp后复发率。\n3. **生活方式指导**：提问饮食、作息、戒烟限酒。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“肝胆风云”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（右上腹痛、向右肩放射、饱餐后发作）。提问：“从患者的描述中，你捕捉到了哪些关键信息呢？”\n2. **分析可能病因**：结合背景信息（肥胖、喜食油腻），提问：“结合患者的背景，你觉得这些表现可能是什么原因导致的？”\n3. **鉴别诊断**：提问：“右上腹痛应考虑哪些疾病？”\n4. **辅助检查选择**：提问：“应首选什么检查确诊？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（中年女性、肥胖、油腻饮食）。\n2. **胆囊结石病因**：提问胆汁成分改变、胆汁淤积等。\n3. **急性胆囊炎病理**：讲解结石嵌顿、细菌感染。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读检查结果**：提问：“B超示胆囊结石，血象高，提示什么？”\n2. **治疗选择**：提问：“保守治疗与手术治疗各自的优缺点？”\n3. **手术时机**：提问：“为什么急性炎症控制后需要择期手术？”\n4. **与患者沟通**：引导学生解释手术必要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **胆囊切除术适应证**：提问有症状的胆囊结石、并发症风险等。\n2. **腹腔镜手术优势**：提问创伤小、恢复快。\n3. **手术风险**：提问胆管损伤、出血、感染等。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **识别并发症**：提问：“术后出现腹痛、发热、黄疸，提示什么？”\n2. **诊断思路**：提问：“如何确诊胆总管残余结石？”\n3. **治疗方案**：提问：“为什么选择ERCP？其优势和风险？”\n4. **与患者沟通**：引导学生向患者解释病情及处理方案。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **胆总管结石成因**：提问胆囊结石掉入胆总管、原发性胆管结石。\n2. **ERCP技术**：讲解取石、括约肌切开等。\n3. **并发症**：提问胰腺炎、穿孔、出血。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“胆囊切除术后饮食如何调整？”\n2. **复发预防**：提问：“如何预防胆管结石复发？”\n3. **长期随访**：提问：“需要复查哪些项目？”\n4. **患者教育**：引导学生回答患者疑问。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **术后消化生理**：讲解胆汁持续排放的影响。\n2. **饮食建议**：提问低脂、高纤维、定时定量。\n3. **定期体检**：提问B超监测。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“肠路惊魂”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（排便习惯改变、便血、消瘦、里急后重）。提问：“从患者的描述中，你捕捉到了哪些关键信息呢？”\n2. **分析危险因素**：结合背景信息（老年、高脂低纤维饮食），提问：“结合患者的背景，你觉得可能是什么问题？”\n3. **鉴别诊断**：提问：“便血原因有哪些？如何区分痔疮与肿瘤？”\n4. **推荐辅助检查**：提问：“应首选哪些检查确诊？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（老年、高脂低纤维饮食）。\n2. **结直肠癌流行病学**：提问发病率、高危人群。\n3. **癌前病变**：提问腺瘤性息肉、溃疡性结肠炎。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读检查结果**：提问：“结肠镜及病理示腺癌，CT示淋巴结转移，说明了什么？”\n2. **分期判断**：提问：“根据结果，临床分期是什么？依据？”\n3. **治疗原则**：提问：“Ⅲ期直肠癌的标准治疗方案是什么？”\n4. **与患者沟通**：引导学生向患者解释病情，安抚恐惧。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **TNM分期**：讲解T、N、M的含义及分期。\n2. **新辅助治疗**：提问局部晚期直肠癌的术前放化疗。\n3. **手术方式**：提问低位前切除术、腹会阴联合切除术。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **解读术后病理**：提问：“淋巴结转移、脉管侵犯，对预后有何影响？”\n2. **辅助化疗指征**：提问：“为什么需要辅助化疗？常用方案？”\n3. **放疗适应证**：提问：“哪些患者需要术后放疗？”\n4. **患者教育**：引导学生解释化疗的必要性和副作用。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **辅助化疗原则**：讲解氟尿嘧啶类、奥沙利铂的作用。\n2. **常见副作用**：提问恶心、骨髓抑制、神经毒性。\n3. **疗效评估**：提问影像学、肿瘤标志物。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“化疗结束后如何随访？”\n2. **随访计划**：提问：“多久复查一次？复查哪些项目？”\n3. **生活方式建议**：提问：“饮食、运动、戒烟限酒？”\n4. **患者教育**：引导学生强调长期随访的重要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **随访指南**：讲解NCCN、CSCO推荐的随访方案。\n2. **复发转移监测**：提问CEA、CT、结肠镜的作用。\n3. **二级预防**：提问健康生活方式、阿司匹林等。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“石破天惊”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（腰腹部绞痛、放射痛、恶心呕吐）。提问：“从患者的描述中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“腰腹痛应考虑哪些急症？”\n3. **辅助检查选择**：提问：“首选的影像学检查是什么？为什么？”\n4. **紧急处理**：提问：“肾绞痛的紧急止痛措施？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（中年男性、体力劳动者、饮水少）。\n2. **泌尿系结石病因**：提问结石形成的危险因素（代谢异常、尿路梗阻、感染等）。\n3. **结石成分**：介绍草酸钙、磷酸钙、尿酸结石等。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读检查结果**：提问：“X线示阳性结石，尿常规红细胞满视野，说明了什么？”\n2. **治疗选择**：提问：“ESWL的适应证？为什么该患者适合？”\n3. **治疗过程解释**：提问：“ESWL后可能出现哪些反应？”\n4. **与患者沟通**：引导学生解释ESWL的必要性和效果。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **ESWL原理**：讲解冲击波聚焦碎石。\n2. **禁忌证**：提问妊娠、凝血障碍、梗阻等。\n3. **并发症**：提问血尿、石街、肾损伤等。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **分析治疗失败**：提问：“ESWL无效的可能原因？”\n2. **后续治疗选择**：提问：“输尿管镜碎石 vs 再次ESWL？”\n3. **手术解释**：提问：“输尿管镜的过程、风险、术后注意事项？”\n4. **患者教育**：引导学生解释再次治疗的必要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **输尿管镜技术**：讲解硬镜、软镜的区别。\n2. **碎石方式**：提问激光、气压弹道。\n3. **并发症**：提问输尿管穿孔、狭窄。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“出院后如何预防结石复发？”\n2. **饮食建议**：提问：“不同成分结石的饮食建议？”\n3. **随访计划**：提问：“多久复查？复查什么？”\n4. **患者教育**：引导学生强调多饮水、定期复查。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **结石预防**：讲解饮水、饮食、药物预防。\n2. **代谢评估**：提问反复发作结石患者的病因筛查。\n3. **长期管理**：提问生活方式干预。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“隐秘的河流”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（水肿、泡沫尿、乏力、高血压）。提问：“从患者的描述和查体中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“水肿、蛋白尿的常见病因？”\n3. **初步检查**：提问：“应首选哪些检查？”\n4. **病情解释**：引导学生向患者解释慢性肾炎的可能性。\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（中年女性、无明确病史）。\n2. **慢性肾炎病理生理**：讲解免疫复合物沉积、肾小球硬化。\n3. **常见病理类型**：提问IgA肾病、膜性肾病等。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读检查结果**：提问：“尿蛋白1.5g/24h，血尿，eGFR 65ml/min，提示什么？”\n2. **诊断确立**：提问：“慢性肾炎的诊断依据？”\n3. **治疗原则**：提问：“ACEI/ARB的作用机制？”\n4. **与患者沟通**：引导学生解释终身服药的必要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **慢性肾炎治疗**：讲解降压、减少蛋白尿、延缓肾损。\n2. **ACEI/ARB的肾脏保护**：提问降低球内压、减少蛋白尿。\n3. **血压控制目标**：提问&lt;130/80mmHg。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **分析病情进展**：提问：“肾功能下降的可能原因？”\n2. **下一步措施**：提问：“是否需要肾活检？加用激素？”\n3. **患者沟通**：引导学生安抚患者，解释积极治疗的意义。\n4. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **肾功能进展因素**：提问蛋白尿水平、血压、病理类型。\n2. **肾活检指征**：提问肾功能快速下降、大量蛋白尿、鉴别诊断。\n3. **免疫抑制剂应用**：提问适应证。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **并发症管理**：提问：“CKD4期需关注哪些并发症？”\n2. **替代治疗准备**：提问：“何时开始准备透析？内瘘何时做？”\n3. **患者教育**：引导学生与患者讨论透析方式、移植等。\n4. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **CKD并发症**：讲解贫血、钙磷代谢紊乱、心血管病。\n2. **透析时机**：提问eGFR&lt;15ml/min或有症状。\n3. **移植评估**：提问HLA配型、等待时间。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“火海警报”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（尿路刺激征、高热、腰痛）。提问：“从患者的描述和查体中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“发热伴尿路症状的常见病？”\n3. **紧急处理**：提问：“高热时应如何处理？”\n4. **辅助检查选择**：提问：“首选的检查是什么？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景信息中找出关键点（年轻女性、劳累、易感因素）。\n2. **尿路感染分类**：提问上尿路与下尿路的区别。\n3. **病原学**：提问大肠杆菌最常见。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读检查结果**：提问：“尿培养示大肠杆菌，药敏敏感，说明了什么？”\n2. **治疗方案**：提问：“抗生素选择原则及疗程？”\n3. **疗效评估**：提问：“退热后仍需治疗多久？”\n4. **与患者沟通**：引导学生解释坚持治疗的重要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **抗生素治疗**：讲解经验性用药与目标治疗。\n2. **疗程**：提问肾盂肾炎10-14天。\n3. **支持治疗**：提问多饮水、休息、对症。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **识别新问题**：提问：“感染控制后仍有腰痛，B超示积水，提示什么？”\n2. **处理原则**：提问：“先控制感染还是先解除梗阻？”\n3. **治疗方案**：提问：“如何解除梗阻？”\n4. **与患者沟通**：引导学生解释处理流程，缓解焦虑。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **感染与结石关系**：讲解结石作为异物加重感染，感染促进结石形成。\n2. **引流方式**：提问输尿管镜、肾造瘘等。\n3. **手术时机**：提问感染控制后手术。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“如何预防尿路感染复发？”\n2. **结石预防**：提问：“感染性结石如何预防？”\n3. **随访建议**：提问：“多久复查尿常规、B超？”\n4. **患者教育**：引导学生强调个人卫生、多饮水、避免憋尿。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **尿路感染易感因素**：讲解女性、性生活、避孕方式等。\n2. **反复感染处理**：提问低剂量抗生素预防、绝经后雌激素。\n3. **长期随访**：提问监测肾功能、影像学。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“折翼天使”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患儿描述中找出关键症状（摔伤后肘部肿痛、不敢活动）。提问：“从患儿的描述和查体中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“儿童肘部外伤应考虑哪些骨折？”\n3. **血管神经评估**：提问：“为什么必须检查桡动脉搏动和手部感觉运动？”\n4. **辅助检查选择**：提问：“应首选什么检查？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患儿背景中找出关键点（儿童、玩耍、摔伤）。\n2. **肱骨髁上骨折解剖**：提问肱骨远端解剖特点及易损伤原因。\n3. **神经血管毗邻关系**：提问正中神经、桡动脉与骨折的关系。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读X线结果**：提问：“骨折移位明显，意味着什么？”\n2. **手术必要性**：提问：“为什么需要急诊手术？保守治疗可以吗？”\n3. **手术风险**：提问：“术中可能损伤哪些结构？”\n4. **与家长沟通**：引导学生解释手术的紧迫性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **骨折分型**：提问伸直型与屈曲型的区别。\n2. **手术方式**：提问切开复位内固定的原理。\n3. **术后护理**：提问石膏固定、抬高患肢。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **识别急症**：提问：“患儿术后疼痛加剧、被动伸指痛、无脉，提示什么？”\n2. **骨筋膜室综合征诊断**：提问“5P征”的内容。\n3. **紧急处理**：提问：“为什么需要立即切开减压？”\n4. **与家长沟通**：引导学生解释紧急手术的紧迫性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **骨筋膜室综合征病理**：讲解筋膜室内压力升高→缺血→坏死。\n2. **好发部位**：提问前臂、小腿最常见。\n3. **后果**：提问缺血性肌挛缩的致残性。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“出院后如何观察患肢血运？”\n2. **康复锻炼**：提问：“何时开始功能锻炼？如何锻炼？”\n3. **远期并发症**：提问：“肘内翻如何预防和处理？”\n4. **家长教育**：引导回答家长问题。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **肘内翻原因**：讲解骨骺损伤、复位不良。\n2. **康复分期**：提问早期被动活动、后期主动活动。\n3. **预防再损伤**：提问安全教育。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“行走的齿轮”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（关节疼痛、活动加重、晨僵短暂）。提问：“从患者的描述和查体中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“如何与类风湿关节炎鉴别？”\n3. **辅助检查**：提问：“应首选什么检查？”\n4. **初步处理**：提问：“急性期可采取哪些措施？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景中找出关键点（老年女性、肥胖、职业）。\n2. **骨关节炎流行病学**：提问年龄、性别、体重的影响。\n3. **关节退变机制**：讲解软骨磨损、骨赘形成。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读X线结果**：提问：“关节间隙变窄、骨赘形成，说明了什么？”\n2. **治疗选择**：提问：“阶梯治疗的含义？该患者处于哪一阶段？”\n3. **药物作用**：提问：“对乙酰氨基酚、非甾体抗炎药的区别？”\n4. **与患者沟通**：引导解释保守治疗的长期性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **骨关节炎非药物治疗**：提问减重、理疗、锻炼。\n2. **关节腔注射**：提问玻璃酸钠、激素的适应证。\n3. **氨基葡萄糖**：提问争议。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **手术指征**：提问：“患者疼痛严重影响生活，X线示终末期改变，应选择什么治疗？”\n2. **人工膝关节置换**：提问：“手术原理？假体类型？”\n3. **并发症预防**：提问：“如何预防DVT、感染？”\n4. **与患者沟通**：引导解释手术风险和预期效果。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **TKA手术过程**：讲解截骨、安装假体。\n2. **假体材料**：提问金属、聚乙烯。\n3. **术后监护**：提问疼痛管理、引流、抗凝。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“出院后如何进行康复锻炼？”\n2. **长期注意事项**：提问：“哪些动作应避免？”\n3. **假体寿命**：提问：“如何延长假体使用寿命？”\n4. **患者教育**：引导强调定期复查、控制体重。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **康复阶段**：讲解术后0-6周、6-12周、3-6月锻炼要点。\n2. **活动限制**：提问避免高冲击运动。\n3. **远期监测**：提问X线评估假体位置、磨损。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“断桥残雪”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（腰痛伴下肢放射痛、咳嗽加重）。提问：“从患者的描述和查体中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“腰痛伴腿痛应考虑哪些疾病？”\n3. **体格检查**：提问：“直腿抬高试验如何操作？有何意义？”\n4. **辅助检查**：提问：“首选什么影像学检查？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景中找出关键点（中年男性、程序员、久坐）。\n2. **椎间盘解剖**：提问纤维环、髓核的结构。\n3. **突出机制**：提问退变、外伤。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读MRI结果**：提问：“L5-S1突出，压迫神经根，与体征是否相符？”\n2. **神经定位**：提问：“足拇趾背伸力减弱提示哪个神经根受累？”\n3. **保守治疗**：提问：“卧床休息、理疗、药物的具体方法？”\n4. **与患者沟通**：引导解释保守治疗的重要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **神经根支配**：讲解L4、L5、S1的运动、感觉、反射。\n2. **非手术治疗**：提问牵引、硬膜外封闭。\n3. **康复训练**：提问腰背肌锻炼。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **识别急症**：提问：“患者出现排尿困难、会阴麻木，提示什么？”\n2. **马尾综合征诊断**：提问：“有哪些典型表现？”\n3. **紧急处理**：提问：“为什么需要急诊手术？最晚何时手术？”\n4. **与家属沟通**：引导解释紧急手术的必要性。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **马尾神经解剖**：提问圆锥、马尾的位置。\n2. **手术方式**：提问椎板切除、髓核摘除。\n3. **预后**：提问大小便功能恢复的可能性。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“术后如何进行腰背肌锻炼？”\n2. **生活注意事项**：提问：“弯腰、坐姿、搬物的正确姿势？”\n3. **预防复发**：提问：“如何避免再次突出？”\n4. **患者教育**：引导强调长期坚持锻炼。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **术后康复分期**：提问早期、中期、晚期活动。\n2. **工作恢复**：提问重返工作时间。\n3. **复发因素**：提问重体力劳动、不良姿势。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“糖衣炮弹”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（多饮、多尿、多食、体重下降）。提问：“从患者的描述中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“多饮多尿还可见于哪些疾病？”\n3. **危险因素**：提问：“高血压史、家族史与糖尿病的关系？”\n4. **辅助检查选择**：提问：“应首选哪些检查确诊？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景中找出关键点（中年男性、高血压、肥胖、家族史）。\n2. **糖尿病分型**：提问1型与2型的区别。\n3. **发病机制**：提问胰岛素抵抗与β细胞功能缺陷。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读检查结果**：提问：“空腹血糖8.5mmol/L，HbA1c 9.2%，说明了什么？”\n2. **治疗原则**：提问：“为什么选择二甲双胍作为一线治疗？”\n3. **血压管理**：提问：“糖尿病合并高血压的治疗目标？”\n4. **与患者沟通**：引导解释二甲双胍的作用和常见副作用。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **二甲双胍机制**：讲解抑制肝糖异生、增加胰岛素敏感性。\n2. **其他口服药**：提问磺脲类、DPP-4抑制剂等。\n3. **糖尿病教育**：提问饮食、运动、血糖监测。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **副作用处理**：提问：“二甲双胍引起胃肠道反应的机制及处理？”\n2. **药物调整**：提问：“不耐受时如何换药？”\n3. **依从性教育**：引导患者理解坚持用药的重要性。\n4. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **药物相互作用**：提问二甲双胍与造影剂、酒精的相互作用。\n2. **禁忌证**：提问肾功能不全、缺氧等。\n3. **联合用药**：提问二甲双胍+磺脲类、+胰岛素等。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“血糖监测频率？糖化血红蛋白控制目标？”\n2. **并发症筛查**：提问：“应定期筛查哪些并发症？”\n3. **生活方式建议**：提问饮食、运动的量化建议。\n4. **患者教育**：引导回答患者关于长期管理的疑问。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **糖尿病慢性并发症**：讲解微血管和大血管并发症。\n2. **随访计划**：提问复查项目及频率。\n3. **低血糖防治**：提问识别和处理。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“隐形狂飙”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（心慌手抖、怕热多汗、消瘦、急躁）。提问：“从患者的描述中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“高代谢表现还可见于哪些情况？”\n3. **体征意义**：提问：“甲状腺肿大伴血管杂音、突眼提示什么？”\n4. **辅助检查选择**：提问：“应首选哪些检查确诊？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景中找出关键点（年轻女性、高代谢、突眼）。\n2. **甲状腺激素生理**：提问甲状腺激素的作用。\n3. **Graves病病因**：提问自身免疫机制。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读检查结果**：提问：“FT3/FT4升高、TSH降低，说明了什么？”\n2. **诊断确立**：提问：“Graves病的诊断依据？”\n3. **治疗选择**：提问：“抗甲状腺药物、放射性碘、手术各自的优缺点？”\n4. **与患者沟通**：引导解释药物选择及注意事项。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **抗甲状腺药物**：讲解甲巯咪唑、丙硫氧嘧啶的作用机制。\n2. **不良反应**：提问皮疹、肝损、粒细胞缺乏。\n3. **β受体阻滞剂**：提问控制症状。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **识别急症**：提问：“咽痛、发热、白细胞减少，提示什么？”\n2. **紧急处理**：提问：“粒细胞缺乏的处理原则？”\n3. **后续治疗**：提问：“换用其他药物或治疗方案？”\n4. **与患者沟通**：引导解释紧急情况和后续调整。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **粒细胞缺乏机制**：讲解免疫介导。\n2. **丙硫氧嘧啶特点**：提问妊娠期使用、肝毒性。\n3. **甲状腺危象**：提问诱因、表现、处理。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **出院指导**：提问：“如何监测药物副作用？”\n2. **治疗疗程**：提问：“抗甲状腺药物总疗程多久？”\n3. **复发预防**：提问：“避免应激、定期复查甲功。”\n4. **患者教育**：引导回答妊娠相关问题。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **甲亢与妊娠**：提问孕前、孕期、产后管理。\n2. **放射性碘治疗**：提问适应证、禁忌证。\n3. **手术指征**：提问巨大甲状腺、压迫症状。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
+  </si>
+  <si>
+    <t>“荷尔蒙迷航”</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（月经稀发、不孕、多毛、肥胖）。提问：“从患者的描述中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“高雄激素表现还可见于哪些疾病？”\n3. **辅助检查选择**：提问：“应做哪些检查明确诊断？”\n4. **初步评估**：提问：“为什么需要评估胰岛素抵抗？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
+  </si>
+  <si>
+    <t>1. **捕捉关键信息**：从患者背景中找出关键点（年轻女性、肥胖、不孕）。\n2. **PCOS病理生理**：讲解高雄激素、胰岛素抵抗、LH/FSH失衡。\n3. **诊断标准**：提问鹿特丹标准。\n4. **总结与预告**：总结背景知识，提示进入问诊。</t>
+  </si>
+  <si>
+    <t>1. **解读检查结果**：提问：“LH/FSH&gt;2，睾酮升高，B超示卵巢多囊，符合PCOS诊断吗？”\n2. **治疗原则**：提问：“为什么生活方式干预是基础？”\n3. **二甲双胍作用**：提问：“改善胰岛素抵抗如何改善排卵？”\n4. **与患者沟通**：引导解释长期管理和耐心。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **PCOS代谢异常**：讲解糖脂代谢紊乱。\n2. **远期风险**：提问糖尿病、心血管病、子宫内膜癌。\n3. **非药物治疗**：提问饮食、运动、减重。\n4. **总结与返回**：提示返回问诊，继续解释。</t>
+  </si>
+  <si>
+    <t>1. **评估疗效**：提问：“减重后仍无排卵，下一步如何处理？”\n2. **促排卵选择**：提问：“克罗米芬的作用机制及用法？”\n3. **并发症**：提问：“OHSS的表现及预防？”\n4. **与患者沟通**：引导解释促排卵过程和风险。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **克罗米芬**：讲解抗雌激素作用。\n2. **其他促排卵药**：提问来曲唑、促性腺激素。\n3. **监测方法**：提问B超、激素。\n4. **总结与返回**：提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **孕期管理**：提问：“PCOS患者孕期需监测什么？”\n2. **药物调整**：提问：“二甲双胍是否继续使用？”\n3. **远期健康**：提问：“产后如何预防远期并发症？”\n4. **患者教育**：引导回答关于宝宝健康、自身健康的问题。\n5. **总结与返回**：总结学习要点，并提示返回问诊。</t>
+  </si>
+  <si>
+    <t>1. **PCOS与妊娠并发症**：讲解GDM、PIH、流产风险。\n2. **产后随访**：提问代谢评估、月经恢复。\n3. **子代健康**：提问对子代远期影响。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
   </si>
 </sst>
 </file>
@@ -1732,7 +2302,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D337"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3989,6 +4559,2470 @@
         <v>185</v>
       </c>
     </row>
+    <row r="162" spans="1:4">
+      <c r="A162" t="s">
+        <v>186</v>
+      </c>
+      <c r="B162">
+        <v>1</v>
+      </c>
+      <c r="C162" t="s">
+        <v>5</v>
+      </c>
+      <c r="D162" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" t="s">
+        <v>186</v>
+      </c>
+      <c r="B163">
+        <v>1</v>
+      </c>
+      <c r="C163" t="s">
+        <v>7</v>
+      </c>
+      <c r="D163" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" t="s">
+        <v>186</v>
+      </c>
+      <c r="B164">
+        <v>2</v>
+      </c>
+      <c r="C164" t="s">
+        <v>5</v>
+      </c>
+      <c r="D164" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" t="s">
+        <v>186</v>
+      </c>
+      <c r="B165">
+        <v>2</v>
+      </c>
+      <c r="C165" t="s">
+        <v>7</v>
+      </c>
+      <c r="D165" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" t="s">
+        <v>186</v>
+      </c>
+      <c r="B166">
+        <v>3</v>
+      </c>
+      <c r="C166" t="s">
+        <v>5</v>
+      </c>
+      <c r="D166" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" t="s">
+        <v>186</v>
+      </c>
+      <c r="B167">
+        <v>3</v>
+      </c>
+      <c r="C167" t="s">
+        <v>7</v>
+      </c>
+      <c r="D167" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" t="s">
+        <v>186</v>
+      </c>
+      <c r="B168">
+        <v>4</v>
+      </c>
+      <c r="C168" t="s">
+        <v>5</v>
+      </c>
+      <c r="D168" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" t="s">
+        <v>186</v>
+      </c>
+      <c r="B169">
+        <v>4</v>
+      </c>
+      <c r="C169" t="s">
+        <v>7</v>
+      </c>
+      <c r="D169" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" t="s">
+        <v>195</v>
+      </c>
+      <c r="B170">
+        <v>1</v>
+      </c>
+      <c r="C170" t="s">
+        <v>5</v>
+      </c>
+      <c r="D170" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" t="s">
+        <v>195</v>
+      </c>
+      <c r="B171">
+        <v>1</v>
+      </c>
+      <c r="C171" t="s">
+        <v>7</v>
+      </c>
+      <c r="D171" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" t="s">
+        <v>195</v>
+      </c>
+      <c r="B172">
+        <v>2</v>
+      </c>
+      <c r="C172" t="s">
+        <v>5</v>
+      </c>
+      <c r="D172" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" t="s">
+        <v>195</v>
+      </c>
+      <c r="B173">
+        <v>2</v>
+      </c>
+      <c r="C173" t="s">
+        <v>7</v>
+      </c>
+      <c r="D173" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" t="s">
+        <v>195</v>
+      </c>
+      <c r="B174">
+        <v>3</v>
+      </c>
+      <c r="C174" t="s">
+        <v>5</v>
+      </c>
+      <c r="D174" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" t="s">
+        <v>195</v>
+      </c>
+      <c r="B175">
+        <v>3</v>
+      </c>
+      <c r="C175" t="s">
+        <v>7</v>
+      </c>
+      <c r="D175" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" t="s">
+        <v>195</v>
+      </c>
+      <c r="B176">
+        <v>4</v>
+      </c>
+      <c r="C176" t="s">
+        <v>5</v>
+      </c>
+      <c r="D176" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" t="s">
+        <v>195</v>
+      </c>
+      <c r="B177">
+        <v>4</v>
+      </c>
+      <c r="C177" t="s">
+        <v>7</v>
+      </c>
+      <c r="D177" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" t="s">
+        <v>196</v>
+      </c>
+      <c r="B178">
+        <v>1</v>
+      </c>
+      <c r="C178" t="s">
+        <v>5</v>
+      </c>
+      <c r="D178" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" t="s">
+        <v>196</v>
+      </c>
+      <c r="B179">
+        <v>1</v>
+      </c>
+      <c r="C179" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" t="s">
+        <v>196</v>
+      </c>
+      <c r="B180">
+        <v>2</v>
+      </c>
+      <c r="C180" t="s">
+        <v>5</v>
+      </c>
+      <c r="D180" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" t="s">
+        <v>196</v>
+      </c>
+      <c r="B181">
+        <v>2</v>
+      </c>
+      <c r="C181" t="s">
+        <v>7</v>
+      </c>
+      <c r="D181" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" t="s">
+        <v>196</v>
+      </c>
+      <c r="B182">
+        <v>3</v>
+      </c>
+      <c r="C182" t="s">
+        <v>5</v>
+      </c>
+      <c r="D182" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" t="s">
+        <v>196</v>
+      </c>
+      <c r="B183">
+        <v>3</v>
+      </c>
+      <c r="C183" t="s">
+        <v>7</v>
+      </c>
+      <c r="D183" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" t="s">
+        <v>196</v>
+      </c>
+      <c r="B184">
+        <v>4</v>
+      </c>
+      <c r="C184" t="s">
+        <v>5</v>
+      </c>
+      <c r="D184" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" t="s">
+        <v>196</v>
+      </c>
+      <c r="B185">
+        <v>4</v>
+      </c>
+      <c r="C185" t="s">
+        <v>7</v>
+      </c>
+      <c r="D185" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" t="s">
+        <v>205</v>
+      </c>
+      <c r="B186">
+        <v>1</v>
+      </c>
+      <c r="C186" t="s">
+        <v>5</v>
+      </c>
+      <c r="D186" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" t="s">
+        <v>205</v>
+      </c>
+      <c r="B187">
+        <v>1</v>
+      </c>
+      <c r="C187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D187" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" t="s">
+        <v>205</v>
+      </c>
+      <c r="B188">
+        <v>2</v>
+      </c>
+      <c r="C188" t="s">
+        <v>5</v>
+      </c>
+      <c r="D188" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" t="s">
+        <v>205</v>
+      </c>
+      <c r="B189">
+        <v>2</v>
+      </c>
+      <c r="C189" t="s">
+        <v>7</v>
+      </c>
+      <c r="D189" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" t="s">
+        <v>205</v>
+      </c>
+      <c r="B190">
+        <v>3</v>
+      </c>
+      <c r="C190" t="s">
+        <v>5</v>
+      </c>
+      <c r="D190" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" t="s">
+        <v>205</v>
+      </c>
+      <c r="B191">
+        <v>3</v>
+      </c>
+      <c r="C191" t="s">
+        <v>7</v>
+      </c>
+      <c r="D191" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" t="s">
+        <v>205</v>
+      </c>
+      <c r="B192">
+        <v>4</v>
+      </c>
+      <c r="C192" t="s">
+        <v>5</v>
+      </c>
+      <c r="D192" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" t="s">
+        <v>205</v>
+      </c>
+      <c r="B193">
+        <v>4</v>
+      </c>
+      <c r="C193" t="s">
+        <v>7</v>
+      </c>
+      <c r="D193" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" t="s">
+        <v>214</v>
+      </c>
+      <c r="B194">
+        <v>1</v>
+      </c>
+      <c r="C194" t="s">
+        <v>5</v>
+      </c>
+      <c r="D194" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" t="s">
+        <v>214</v>
+      </c>
+      <c r="B195">
+        <v>1</v>
+      </c>
+      <c r="C195" t="s">
+        <v>7</v>
+      </c>
+      <c r="D195" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" t="s">
+        <v>214</v>
+      </c>
+      <c r="B196">
+        <v>2</v>
+      </c>
+      <c r="C196" t="s">
+        <v>5</v>
+      </c>
+      <c r="D196" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" t="s">
+        <v>214</v>
+      </c>
+      <c r="B197">
+        <v>2</v>
+      </c>
+      <c r="C197" t="s">
+        <v>7</v>
+      </c>
+      <c r="D197" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" t="s">
+        <v>214</v>
+      </c>
+      <c r="B198">
+        <v>3</v>
+      </c>
+      <c r="C198" t="s">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" t="s">
+        <v>214</v>
+      </c>
+      <c r="B199">
+        <v>3</v>
+      </c>
+      <c r="C199" t="s">
+        <v>7</v>
+      </c>
+      <c r="D199" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" t="s">
+        <v>214</v>
+      </c>
+      <c r="B200">
+        <v>4</v>
+      </c>
+      <c r="C200" t="s">
+        <v>5</v>
+      </c>
+      <c r="D200" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" t="s">
+        <v>214</v>
+      </c>
+      <c r="B201">
+        <v>4</v>
+      </c>
+      <c r="C201" t="s">
+        <v>7</v>
+      </c>
+      <c r="D201" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" t="s">
+        <v>223</v>
+      </c>
+      <c r="B202">
+        <v>1</v>
+      </c>
+      <c r="C202" t="s">
+        <v>5</v>
+      </c>
+      <c r="D202" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" t="s">
+        <v>223</v>
+      </c>
+      <c r="B203">
+        <v>1</v>
+      </c>
+      <c r="C203" t="s">
+        <v>7</v>
+      </c>
+      <c r="D203" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" t="s">
+        <v>223</v>
+      </c>
+      <c r="B204">
+        <v>2</v>
+      </c>
+      <c r="C204" t="s">
+        <v>5</v>
+      </c>
+      <c r="D204" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" t="s">
+        <v>223</v>
+      </c>
+      <c r="B205">
+        <v>2</v>
+      </c>
+      <c r="C205" t="s">
+        <v>7</v>
+      </c>
+      <c r="D205" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" t="s">
+        <v>223</v>
+      </c>
+      <c r="B206">
+        <v>3</v>
+      </c>
+      <c r="C206" t="s">
+        <v>5</v>
+      </c>
+      <c r="D206" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" t="s">
+        <v>223</v>
+      </c>
+      <c r="B207">
+        <v>3</v>
+      </c>
+      <c r="C207" t="s">
+        <v>7</v>
+      </c>
+      <c r="D207" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" t="s">
+        <v>223</v>
+      </c>
+      <c r="B208">
+        <v>4</v>
+      </c>
+      <c r="C208" t="s">
+        <v>5</v>
+      </c>
+      <c r="D208" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" t="s">
+        <v>223</v>
+      </c>
+      <c r="B209">
+        <v>4</v>
+      </c>
+      <c r="C209" t="s">
+        <v>7</v>
+      </c>
+      <c r="D209" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" t="s">
+        <v>232</v>
+      </c>
+      <c r="B210">
+        <v>1</v>
+      </c>
+      <c r="C210" t="s">
+        <v>5</v>
+      </c>
+      <c r="D210" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" t="s">
+        <v>232</v>
+      </c>
+      <c r="B211">
+        <v>1</v>
+      </c>
+      <c r="C211" t="s">
+        <v>7</v>
+      </c>
+      <c r="D211" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" t="s">
+        <v>232</v>
+      </c>
+      <c r="B212">
+        <v>2</v>
+      </c>
+      <c r="C212" t="s">
+        <v>5</v>
+      </c>
+      <c r="D212" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" t="s">
+        <v>232</v>
+      </c>
+      <c r="B213">
+        <v>2</v>
+      </c>
+      <c r="C213" t="s">
+        <v>7</v>
+      </c>
+      <c r="D213" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" t="s">
+        <v>232</v>
+      </c>
+      <c r="B214">
+        <v>3</v>
+      </c>
+      <c r="C214" t="s">
+        <v>5</v>
+      </c>
+      <c r="D214" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" t="s">
+        <v>232</v>
+      </c>
+      <c r="B215">
+        <v>3</v>
+      </c>
+      <c r="C215" t="s">
+        <v>7</v>
+      </c>
+      <c r="D215" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" t="s">
+        <v>232</v>
+      </c>
+      <c r="B216">
+        <v>4</v>
+      </c>
+      <c r="C216" t="s">
+        <v>5</v>
+      </c>
+      <c r="D216" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" t="s">
+        <v>232</v>
+      </c>
+      <c r="B217">
+        <v>4</v>
+      </c>
+      <c r="C217" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" t="s">
+        <v>241</v>
+      </c>
+      <c r="B218">
+        <v>1</v>
+      </c>
+      <c r="C218" t="s">
+        <v>5</v>
+      </c>
+      <c r="D218" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" t="s">
+        <v>241</v>
+      </c>
+      <c r="B219">
+        <v>1</v>
+      </c>
+      <c r="C219" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" t="s">
+        <v>241</v>
+      </c>
+      <c r="B220">
+        <v>2</v>
+      </c>
+      <c r="C220" t="s">
+        <v>5</v>
+      </c>
+      <c r="D220" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" t="s">
+        <v>241</v>
+      </c>
+      <c r="B221">
+        <v>2</v>
+      </c>
+      <c r="C221" t="s">
+        <v>7</v>
+      </c>
+      <c r="D221" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" t="s">
+        <v>241</v>
+      </c>
+      <c r="B222">
+        <v>3</v>
+      </c>
+      <c r="C222" t="s">
+        <v>5</v>
+      </c>
+      <c r="D222" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" t="s">
+        <v>241</v>
+      </c>
+      <c r="B223">
+        <v>3</v>
+      </c>
+      <c r="C223" t="s">
+        <v>7</v>
+      </c>
+      <c r="D223" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" t="s">
+        <v>241</v>
+      </c>
+      <c r="B224">
+        <v>4</v>
+      </c>
+      <c r="C224" t="s">
+        <v>5</v>
+      </c>
+      <c r="D224" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" t="s">
+        <v>241</v>
+      </c>
+      <c r="B225">
+        <v>4</v>
+      </c>
+      <c r="C225" t="s">
+        <v>7</v>
+      </c>
+      <c r="D225" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" t="s">
+        <v>250</v>
+      </c>
+      <c r="B226">
+        <v>1</v>
+      </c>
+      <c r="C226" t="s">
+        <v>5</v>
+      </c>
+      <c r="D226" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" t="s">
+        <v>250</v>
+      </c>
+      <c r="B227">
+        <v>1</v>
+      </c>
+      <c r="C227" t="s">
+        <v>7</v>
+      </c>
+      <c r="D227" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" t="s">
+        <v>250</v>
+      </c>
+      <c r="B228">
+        <v>2</v>
+      </c>
+      <c r="C228" t="s">
+        <v>5</v>
+      </c>
+      <c r="D228" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" t="s">
+        <v>250</v>
+      </c>
+      <c r="B229">
+        <v>2</v>
+      </c>
+      <c r="C229" t="s">
+        <v>7</v>
+      </c>
+      <c r="D229" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" t="s">
+        <v>250</v>
+      </c>
+      <c r="B230">
+        <v>3</v>
+      </c>
+      <c r="C230" t="s">
+        <v>5</v>
+      </c>
+      <c r="D230" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" t="s">
+        <v>250</v>
+      </c>
+      <c r="B231">
+        <v>3</v>
+      </c>
+      <c r="C231" t="s">
+        <v>7</v>
+      </c>
+      <c r="D231" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" t="s">
+        <v>250</v>
+      </c>
+      <c r="B232">
+        <v>4</v>
+      </c>
+      <c r="C232" t="s">
+        <v>5</v>
+      </c>
+      <c r="D232" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" t="s">
+        <v>250</v>
+      </c>
+      <c r="B233">
+        <v>4</v>
+      </c>
+      <c r="C233" t="s">
+        <v>7</v>
+      </c>
+      <c r="D233" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" t="s">
+        <v>259</v>
+      </c>
+      <c r="B234">
+        <v>1</v>
+      </c>
+      <c r="C234" t="s">
+        <v>5</v>
+      </c>
+      <c r="D234" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" t="s">
+        <v>259</v>
+      </c>
+      <c r="B235">
+        <v>1</v>
+      </c>
+      <c r="C235" t="s">
+        <v>7</v>
+      </c>
+      <c r="D235" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" t="s">
+        <v>259</v>
+      </c>
+      <c r="B236">
+        <v>2</v>
+      </c>
+      <c r="C236" t="s">
+        <v>5</v>
+      </c>
+      <c r="D236" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" t="s">
+        <v>259</v>
+      </c>
+      <c r="B237">
+        <v>2</v>
+      </c>
+      <c r="C237" t="s">
+        <v>7</v>
+      </c>
+      <c r="D237" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" t="s">
+        <v>259</v>
+      </c>
+      <c r="B238">
+        <v>3</v>
+      </c>
+      <c r="C238" t="s">
+        <v>5</v>
+      </c>
+      <c r="D238" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
+        <v>259</v>
+      </c>
+      <c r="B239">
+        <v>3</v>
+      </c>
+      <c r="C239" t="s">
+        <v>7</v>
+      </c>
+      <c r="D239" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
+        <v>259</v>
+      </c>
+      <c r="B240">
+        <v>4</v>
+      </c>
+      <c r="C240" t="s">
+        <v>5</v>
+      </c>
+      <c r="D240" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
+        <v>259</v>
+      </c>
+      <c r="B241">
+        <v>4</v>
+      </c>
+      <c r="C241" t="s">
+        <v>7</v>
+      </c>
+      <c r="D241" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
+        <v>268</v>
+      </c>
+      <c r="B242">
+        <v>1</v>
+      </c>
+      <c r="C242" t="s">
+        <v>5</v>
+      </c>
+      <c r="D242" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" t="s">
+        <v>268</v>
+      </c>
+      <c r="B243">
+        <v>1</v>
+      </c>
+      <c r="C243" t="s">
+        <v>7</v>
+      </c>
+      <c r="D243" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" t="s">
+        <v>268</v>
+      </c>
+      <c r="B244">
+        <v>2</v>
+      </c>
+      <c r="C244" t="s">
+        <v>5</v>
+      </c>
+      <c r="D244" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" t="s">
+        <v>268</v>
+      </c>
+      <c r="B245">
+        <v>2</v>
+      </c>
+      <c r="C245" t="s">
+        <v>7</v>
+      </c>
+      <c r="D245" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" t="s">
+        <v>268</v>
+      </c>
+      <c r="B246">
+        <v>3</v>
+      </c>
+      <c r="C246" t="s">
+        <v>5</v>
+      </c>
+      <c r="D246" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" t="s">
+        <v>268</v>
+      </c>
+      <c r="B247">
+        <v>3</v>
+      </c>
+      <c r="C247" t="s">
+        <v>7</v>
+      </c>
+      <c r="D247" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" t="s">
+        <v>268</v>
+      </c>
+      <c r="B248">
+        <v>4</v>
+      </c>
+      <c r="C248" t="s">
+        <v>5</v>
+      </c>
+      <c r="D248" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" t="s">
+        <v>268</v>
+      </c>
+      <c r="B249">
+        <v>4</v>
+      </c>
+      <c r="C249" t="s">
+        <v>7</v>
+      </c>
+      <c r="D249" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" t="s">
+        <v>277</v>
+      </c>
+      <c r="B250">
+        <v>1</v>
+      </c>
+      <c r="C250" t="s">
+        <v>5</v>
+      </c>
+      <c r="D250" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" t="s">
+        <v>277</v>
+      </c>
+      <c r="B251">
+        <v>1</v>
+      </c>
+      <c r="C251" t="s">
+        <v>7</v>
+      </c>
+      <c r="D251" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" t="s">
+        <v>277</v>
+      </c>
+      <c r="B252">
+        <v>2</v>
+      </c>
+      <c r="C252" t="s">
+        <v>5</v>
+      </c>
+      <c r="D252" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" t="s">
+        <v>277</v>
+      </c>
+      <c r="B253">
+        <v>2</v>
+      </c>
+      <c r="C253" t="s">
+        <v>7</v>
+      </c>
+      <c r="D253" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" t="s">
+        <v>277</v>
+      </c>
+      <c r="B254">
+        <v>3</v>
+      </c>
+      <c r="C254" t="s">
+        <v>5</v>
+      </c>
+      <c r="D254" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" t="s">
+        <v>277</v>
+      </c>
+      <c r="B255">
+        <v>3</v>
+      </c>
+      <c r="C255" t="s">
+        <v>7</v>
+      </c>
+      <c r="D255" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" t="s">
+        <v>277</v>
+      </c>
+      <c r="B256">
+        <v>4</v>
+      </c>
+      <c r="C256" t="s">
+        <v>5</v>
+      </c>
+      <c r="D256" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" t="s">
+        <v>277</v>
+      </c>
+      <c r="B257">
+        <v>4</v>
+      </c>
+      <c r="C257" t="s">
+        <v>7</v>
+      </c>
+      <c r="D257" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" t="s">
+        <v>286</v>
+      </c>
+      <c r="B258">
+        <v>1</v>
+      </c>
+      <c r="C258" t="s">
+        <v>5</v>
+      </c>
+      <c r="D258" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" t="s">
+        <v>286</v>
+      </c>
+      <c r="B259">
+        <v>1</v>
+      </c>
+      <c r="C259" t="s">
+        <v>7</v>
+      </c>
+      <c r="D259" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" t="s">
+        <v>286</v>
+      </c>
+      <c r="B260">
+        <v>2</v>
+      </c>
+      <c r="C260" t="s">
+        <v>5</v>
+      </c>
+      <c r="D260" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" t="s">
+        <v>286</v>
+      </c>
+      <c r="B261">
+        <v>2</v>
+      </c>
+      <c r="C261" t="s">
+        <v>7</v>
+      </c>
+      <c r="D261" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" t="s">
+        <v>286</v>
+      </c>
+      <c r="B262">
+        <v>3</v>
+      </c>
+      <c r="C262" t="s">
+        <v>5</v>
+      </c>
+      <c r="D262" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" t="s">
+        <v>286</v>
+      </c>
+      <c r="B263">
+        <v>3</v>
+      </c>
+      <c r="C263" t="s">
+        <v>7</v>
+      </c>
+      <c r="D263" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" t="s">
+        <v>286</v>
+      </c>
+      <c r="B264">
+        <v>4</v>
+      </c>
+      <c r="C264" t="s">
+        <v>5</v>
+      </c>
+      <c r="D264" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" t="s">
+        <v>286</v>
+      </c>
+      <c r="B265">
+        <v>4</v>
+      </c>
+      <c r="C265" t="s">
+        <v>7</v>
+      </c>
+      <c r="D265" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" t="s">
+        <v>295</v>
+      </c>
+      <c r="B266">
+        <v>1</v>
+      </c>
+      <c r="C266" t="s">
+        <v>5</v>
+      </c>
+      <c r="D266" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" t="s">
+        <v>295</v>
+      </c>
+      <c r="B267">
+        <v>1</v>
+      </c>
+      <c r="C267" t="s">
+        <v>7</v>
+      </c>
+      <c r="D267" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" t="s">
+        <v>295</v>
+      </c>
+      <c r="B268">
+        <v>2</v>
+      </c>
+      <c r="C268" t="s">
+        <v>5</v>
+      </c>
+      <c r="D268" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" t="s">
+        <v>295</v>
+      </c>
+      <c r="B269">
+        <v>2</v>
+      </c>
+      <c r="C269" t="s">
+        <v>7</v>
+      </c>
+      <c r="D269" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" t="s">
+        <v>295</v>
+      </c>
+      <c r="B270">
+        <v>3</v>
+      </c>
+      <c r="C270" t="s">
+        <v>5</v>
+      </c>
+      <c r="D270" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" t="s">
+        <v>295</v>
+      </c>
+      <c r="B271">
+        <v>3</v>
+      </c>
+      <c r="C271" t="s">
+        <v>7</v>
+      </c>
+      <c r="D271" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" t="s">
+        <v>295</v>
+      </c>
+      <c r="B272">
+        <v>4</v>
+      </c>
+      <c r="C272" t="s">
+        <v>5</v>
+      </c>
+      <c r="D272" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" t="s">
+        <v>295</v>
+      </c>
+      <c r="B273">
+        <v>4</v>
+      </c>
+      <c r="C273" t="s">
+        <v>7</v>
+      </c>
+      <c r="D273" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" t="s">
+        <v>304</v>
+      </c>
+      <c r="B274">
+        <v>1</v>
+      </c>
+      <c r="C274" t="s">
+        <v>5</v>
+      </c>
+      <c r="D274" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" t="s">
+        <v>304</v>
+      </c>
+      <c r="B275">
+        <v>1</v>
+      </c>
+      <c r="C275" t="s">
+        <v>7</v>
+      </c>
+      <c r="D275" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" t="s">
+        <v>304</v>
+      </c>
+      <c r="B276">
+        <v>2</v>
+      </c>
+      <c r="C276" t="s">
+        <v>5</v>
+      </c>
+      <c r="D276" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" t="s">
+        <v>304</v>
+      </c>
+      <c r="B277">
+        <v>2</v>
+      </c>
+      <c r="C277" t="s">
+        <v>7</v>
+      </c>
+      <c r="D277" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" t="s">
+        <v>304</v>
+      </c>
+      <c r="B278">
+        <v>3</v>
+      </c>
+      <c r="C278" t="s">
+        <v>5</v>
+      </c>
+      <c r="D278" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" t="s">
+        <v>304</v>
+      </c>
+      <c r="B279">
+        <v>3</v>
+      </c>
+      <c r="C279" t="s">
+        <v>7</v>
+      </c>
+      <c r="D279" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" t="s">
+        <v>304</v>
+      </c>
+      <c r="B280">
+        <v>4</v>
+      </c>
+      <c r="C280" t="s">
+        <v>5</v>
+      </c>
+      <c r="D280" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" t="s">
+        <v>304</v>
+      </c>
+      <c r="B281">
+        <v>4</v>
+      </c>
+      <c r="C281" t="s">
+        <v>7</v>
+      </c>
+      <c r="D281" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" t="s">
+        <v>313</v>
+      </c>
+      <c r="B282">
+        <v>1</v>
+      </c>
+      <c r="C282" t="s">
+        <v>5</v>
+      </c>
+      <c r="D282" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" t="s">
+        <v>313</v>
+      </c>
+      <c r="B283">
+        <v>1</v>
+      </c>
+      <c r="C283" t="s">
+        <v>7</v>
+      </c>
+      <c r="D283" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" t="s">
+        <v>313</v>
+      </c>
+      <c r="B284">
+        <v>2</v>
+      </c>
+      <c r="C284" t="s">
+        <v>5</v>
+      </c>
+      <c r="D284" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" t="s">
+        <v>313</v>
+      </c>
+      <c r="B285">
+        <v>2</v>
+      </c>
+      <c r="C285" t="s">
+        <v>7</v>
+      </c>
+      <c r="D285" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" t="s">
+        <v>313</v>
+      </c>
+      <c r="B286">
+        <v>3</v>
+      </c>
+      <c r="C286" t="s">
+        <v>5</v>
+      </c>
+      <c r="D286" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" t="s">
+        <v>313</v>
+      </c>
+      <c r="B287">
+        <v>3</v>
+      </c>
+      <c r="C287" t="s">
+        <v>7</v>
+      </c>
+      <c r="D287" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" t="s">
+        <v>313</v>
+      </c>
+      <c r="B288">
+        <v>4</v>
+      </c>
+      <c r="C288" t="s">
+        <v>5</v>
+      </c>
+      <c r="D288" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" t="s">
+        <v>313</v>
+      </c>
+      <c r="B289">
+        <v>4</v>
+      </c>
+      <c r="C289" t="s">
+        <v>7</v>
+      </c>
+      <c r="D289" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" t="s">
+        <v>322</v>
+      </c>
+      <c r="B290">
+        <v>1</v>
+      </c>
+      <c r="C290" t="s">
+        <v>5</v>
+      </c>
+      <c r="D290" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" t="s">
+        <v>322</v>
+      </c>
+      <c r="B291">
+        <v>1</v>
+      </c>
+      <c r="C291" t="s">
+        <v>7</v>
+      </c>
+      <c r="D291" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" t="s">
+        <v>322</v>
+      </c>
+      <c r="B292">
+        <v>2</v>
+      </c>
+      <c r="C292" t="s">
+        <v>5</v>
+      </c>
+      <c r="D292" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" t="s">
+        <v>322</v>
+      </c>
+      <c r="B293">
+        <v>2</v>
+      </c>
+      <c r="C293" t="s">
+        <v>7</v>
+      </c>
+      <c r="D293" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" t="s">
+        <v>322</v>
+      </c>
+      <c r="B294">
+        <v>3</v>
+      </c>
+      <c r="C294" t="s">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" t="s">
+        <v>322</v>
+      </c>
+      <c r="B295">
+        <v>3</v>
+      </c>
+      <c r="C295" t="s">
+        <v>7</v>
+      </c>
+      <c r="D295" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" t="s">
+        <v>322</v>
+      </c>
+      <c r="B296">
+        <v>4</v>
+      </c>
+      <c r="C296" t="s">
+        <v>5</v>
+      </c>
+      <c r="D296" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" t="s">
+        <v>322</v>
+      </c>
+      <c r="B297">
+        <v>4</v>
+      </c>
+      <c r="C297" t="s">
+        <v>7</v>
+      </c>
+      <c r="D297" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" t="s">
+        <v>331</v>
+      </c>
+      <c r="B298">
+        <v>1</v>
+      </c>
+      <c r="C298" t="s">
+        <v>5</v>
+      </c>
+      <c r="D298" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" t="s">
+        <v>331</v>
+      </c>
+      <c r="B299">
+        <v>1</v>
+      </c>
+      <c r="C299" t="s">
+        <v>7</v>
+      </c>
+      <c r="D299" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" t="s">
+        <v>331</v>
+      </c>
+      <c r="B300">
+        <v>2</v>
+      </c>
+      <c r="C300" t="s">
+        <v>5</v>
+      </c>
+      <c r="D300" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" t="s">
+        <v>331</v>
+      </c>
+      <c r="B301">
+        <v>2</v>
+      </c>
+      <c r="C301" t="s">
+        <v>7</v>
+      </c>
+      <c r="D301" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" t="s">
+        <v>331</v>
+      </c>
+      <c r="B302">
+        <v>3</v>
+      </c>
+      <c r="C302" t="s">
+        <v>5</v>
+      </c>
+      <c r="D302" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" t="s">
+        <v>331</v>
+      </c>
+      <c r="B303">
+        <v>3</v>
+      </c>
+      <c r="C303" t="s">
+        <v>7</v>
+      </c>
+      <c r="D303" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" t="s">
+        <v>331</v>
+      </c>
+      <c r="B304">
+        <v>4</v>
+      </c>
+      <c r="C304" t="s">
+        <v>5</v>
+      </c>
+      <c r="D304" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" t="s">
+        <v>331</v>
+      </c>
+      <c r="B305">
+        <v>4</v>
+      </c>
+      <c r="C305" t="s">
+        <v>7</v>
+      </c>
+      <c r="D305" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" t="s">
+        <v>340</v>
+      </c>
+      <c r="B306">
+        <v>1</v>
+      </c>
+      <c r="C306" t="s">
+        <v>5</v>
+      </c>
+      <c r="D306" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" t="s">
+        <v>340</v>
+      </c>
+      <c r="B307">
+        <v>1</v>
+      </c>
+      <c r="C307" t="s">
+        <v>7</v>
+      </c>
+      <c r="D307" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" t="s">
+        <v>340</v>
+      </c>
+      <c r="B308">
+        <v>2</v>
+      </c>
+      <c r="C308" t="s">
+        <v>5</v>
+      </c>
+      <c r="D308" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" t="s">
+        <v>340</v>
+      </c>
+      <c r="B309">
+        <v>2</v>
+      </c>
+      <c r="C309" t="s">
+        <v>7</v>
+      </c>
+      <c r="D309" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" t="s">
+        <v>340</v>
+      </c>
+      <c r="B310">
+        <v>3</v>
+      </c>
+      <c r="C310" t="s">
+        <v>5</v>
+      </c>
+      <c r="D310" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" t="s">
+        <v>340</v>
+      </c>
+      <c r="B311">
+        <v>3</v>
+      </c>
+      <c r="C311" t="s">
+        <v>7</v>
+      </c>
+      <c r="D311" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" t="s">
+        <v>340</v>
+      </c>
+      <c r="B312">
+        <v>4</v>
+      </c>
+      <c r="C312" t="s">
+        <v>5</v>
+      </c>
+      <c r="D312" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" t="s">
+        <v>340</v>
+      </c>
+      <c r="B313">
+        <v>4</v>
+      </c>
+      <c r="C313" t="s">
+        <v>7</v>
+      </c>
+      <c r="D313" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" t="s">
+        <v>349</v>
+      </c>
+      <c r="B314">
+        <v>1</v>
+      </c>
+      <c r="C314" t="s">
+        <v>5</v>
+      </c>
+      <c r="D314" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" t="s">
+        <v>349</v>
+      </c>
+      <c r="B315">
+        <v>1</v>
+      </c>
+      <c r="C315" t="s">
+        <v>7</v>
+      </c>
+      <c r="D315" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" t="s">
+        <v>349</v>
+      </c>
+      <c r="B316">
+        <v>2</v>
+      </c>
+      <c r="C316" t="s">
+        <v>5</v>
+      </c>
+      <c r="D316" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" t="s">
+        <v>349</v>
+      </c>
+      <c r="B317">
+        <v>2</v>
+      </c>
+      <c r="C317" t="s">
+        <v>7</v>
+      </c>
+      <c r="D317" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" t="s">
+        <v>349</v>
+      </c>
+      <c r="B318">
+        <v>3</v>
+      </c>
+      <c r="C318" t="s">
+        <v>5</v>
+      </c>
+      <c r="D318" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" t="s">
+        <v>349</v>
+      </c>
+      <c r="B319">
+        <v>3</v>
+      </c>
+      <c r="C319" t="s">
+        <v>7</v>
+      </c>
+      <c r="D319" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" t="s">
+        <v>349</v>
+      </c>
+      <c r="B320">
+        <v>4</v>
+      </c>
+      <c r="C320" t="s">
+        <v>5</v>
+      </c>
+      <c r="D320" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" t="s">
+        <v>349</v>
+      </c>
+      <c r="B321">
+        <v>4</v>
+      </c>
+      <c r="C321" t="s">
+        <v>7</v>
+      </c>
+      <c r="D321" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" t="s">
+        <v>358</v>
+      </c>
+      <c r="B322">
+        <v>1</v>
+      </c>
+      <c r="C322" t="s">
+        <v>5</v>
+      </c>
+      <c r="D322" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" t="s">
+        <v>358</v>
+      </c>
+      <c r="B323">
+        <v>1</v>
+      </c>
+      <c r="C323" t="s">
+        <v>7</v>
+      </c>
+      <c r="D323" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" t="s">
+        <v>358</v>
+      </c>
+      <c r="B324">
+        <v>2</v>
+      </c>
+      <c r="C324" t="s">
+        <v>5</v>
+      </c>
+      <c r="D324" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" t="s">
+        <v>358</v>
+      </c>
+      <c r="B325">
+        <v>2</v>
+      </c>
+      <c r="C325" t="s">
+        <v>7</v>
+      </c>
+      <c r="D325" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" t="s">
+        <v>358</v>
+      </c>
+      <c r="B326">
+        <v>3</v>
+      </c>
+      <c r="C326" t="s">
+        <v>5</v>
+      </c>
+      <c r="D326" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" t="s">
+        <v>358</v>
+      </c>
+      <c r="B327">
+        <v>3</v>
+      </c>
+      <c r="C327" t="s">
+        <v>7</v>
+      </c>
+      <c r="D327" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" t="s">
+        <v>358</v>
+      </c>
+      <c r="B328">
+        <v>4</v>
+      </c>
+      <c r="C328" t="s">
+        <v>5</v>
+      </c>
+      <c r="D328" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" t="s">
+        <v>358</v>
+      </c>
+      <c r="B329">
+        <v>4</v>
+      </c>
+      <c r="C329" t="s">
+        <v>7</v>
+      </c>
+      <c r="D329" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" t="s">
+        <v>367</v>
+      </c>
+      <c r="B330">
+        <v>1</v>
+      </c>
+      <c r="C330" t="s">
+        <v>5</v>
+      </c>
+      <c r="D330" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" t="s">
+        <v>367</v>
+      </c>
+      <c r="B331">
+        <v>1</v>
+      </c>
+      <c r="C331" t="s">
+        <v>7</v>
+      </c>
+      <c r="D331" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" t="s">
+        <v>367</v>
+      </c>
+      <c r="B332">
+        <v>2</v>
+      </c>
+      <c r="C332" t="s">
+        <v>5</v>
+      </c>
+      <c r="D332" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" t="s">
+        <v>367</v>
+      </c>
+      <c r="B333">
+        <v>2</v>
+      </c>
+      <c r="C333" t="s">
+        <v>7</v>
+      </c>
+      <c r="D333" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" t="s">
+        <v>367</v>
+      </c>
+      <c r="B334">
+        <v>3</v>
+      </c>
+      <c r="C334" t="s">
+        <v>5</v>
+      </c>
+      <c r="D334" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" t="s">
+        <v>367</v>
+      </c>
+      <c r="B335">
+        <v>3</v>
+      </c>
+      <c r="C335" t="s">
+        <v>7</v>
+      </c>
+      <c r="D335" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" t="s">
+        <v>367</v>
+      </c>
+      <c r="B336">
+        <v>4</v>
+      </c>
+      <c r="C336" t="s">
+        <v>5</v>
+      </c>
+      <c r="D336" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" t="s">
+        <v>367</v>
+      </c>
+      <c r="B337">
+        <v>4</v>
+      </c>
+      <c r="C337" t="s">
+        <v>7</v>
+      </c>
+      <c r="D337" t="s">
+        <v>375</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data/医小星教学大纲.xlsx
+++ b/data/医小星教学大纲.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="375">
   <si>
     <t>疾病</t>
   </si>
@@ -587,7 +587,7 @@
     <t>1. **肺癌驱动基因**：讲解EGFR、ALK等检测的必要性。\n2. **骨转移的局部治疗**：提问放疗、双膦酸盐的应用。\n3. **支持治疗**：提问止痛、营养、心理支持。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
   </si>
   <si>
-    <t>“脑中风的警报”</t>
+    <t>“半身风云”</t>
   </si>
   <si>
     <t>1. **捕捉关键信息**：引导学生从患者描述中找出关键症状（突发偏瘫、失语、高血压史）。提问：“从患者的描述和查体中，你捕捉到了哪些关键信息呢？”\n2. **鉴别诊断**：提问：“突发神经系统功能障碍，应首先区分缺血还是出血？如何快速鉴别？”\n3. **紧急处理**：提问：“在等待影像学结果时，应采取哪些基本措施？”\n4. **辅助检查选择**：提问：“首选什么检查？为什么？”\n5. **总结与返回**：总结学习要点，并提示可以返回问诊继续和患者对话。</t>
@@ -612,9 +612,6 @@
   </si>
   <si>
     <t>1. **随访计划**：讲解复查频率及项目。\n2. **二级预防指南**：提问国内外指南推荐。\n3. **家庭护理**：提问家属如何协助康复。\n4. **总结与返回**：提示返回问诊，向患者交代。</t>
-  </si>
-  <si>
-    <t>“半身风云”</t>
   </si>
   <si>
     <t>“惊厥之舞”</t>
@@ -2302,7 +2299,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D337"/>
+  <dimension ref="A1:D329"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -4682,7 +4679,7 @@
         <v>5</v>
       </c>
       <c r="D170" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4696,7 +4693,7 @@
         <v>7</v>
       </c>
       <c r="D171" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4710,7 +4707,7 @@
         <v>5</v>
       </c>
       <c r="D172" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4724,7 +4721,7 @@
         <v>7</v>
       </c>
       <c r="D173" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4738,7 +4735,7 @@
         <v>5</v>
       </c>
       <c r="D174" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4752,7 +4749,7 @@
         <v>7</v>
       </c>
       <c r="D175" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4766,7 +4763,7 @@
         <v>5</v>
       </c>
       <c r="D176" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4780,12 +4777,12 @@
         <v>7</v>
       </c>
       <c r="D177" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -4794,12 +4791,12 @@
         <v>5</v>
       </c>
       <c r="D178" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -4808,12 +4805,12 @@
         <v>7</v>
       </c>
       <c r="D179" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B180">
         <v>2</v>
@@ -4822,12 +4819,12 @@
         <v>5</v>
       </c>
       <c r="D180" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B181">
         <v>2</v>
@@ -4836,12 +4833,12 @@
         <v>7</v>
       </c>
       <c r="D181" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B182">
         <v>3</v>
@@ -4850,12 +4847,12 @@
         <v>5</v>
       </c>
       <c r="D182" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B183">
         <v>3</v>
@@ -4864,12 +4861,12 @@
         <v>7</v>
       </c>
       <c r="D183" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B184">
         <v>4</v>
@@ -4878,12 +4875,12 @@
         <v>5</v>
       </c>
       <c r="D184" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B185">
         <v>4</v>
@@ -4892,12 +4889,12 @@
         <v>7</v>
       </c>
       <c r="D185" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -4906,12 +4903,12 @@
         <v>5</v>
       </c>
       <c r="D186" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -4920,12 +4917,12 @@
         <v>7</v>
       </c>
       <c r="D187" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B188">
         <v>2</v>
@@ -4934,12 +4931,12 @@
         <v>5</v>
       </c>
       <c r="D188" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B189">
         <v>2</v>
@@ -4948,12 +4945,12 @@
         <v>7</v>
       </c>
       <c r="D189" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B190">
         <v>3</v>
@@ -4962,12 +4959,12 @@
         <v>5</v>
       </c>
       <c r="D190" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B191">
         <v>3</v>
@@ -4976,12 +4973,12 @@
         <v>7</v>
       </c>
       <c r="D191" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B192">
         <v>4</v>
@@ -4990,12 +4987,12 @@
         <v>5</v>
       </c>
       <c r="D192" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B193">
         <v>4</v>
@@ -5004,12 +5001,12 @@
         <v>7</v>
       </c>
       <c r="D193" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -5018,12 +5015,12 @@
         <v>5</v>
       </c>
       <c r="D194" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -5032,12 +5029,12 @@
         <v>7</v>
       </c>
       <c r="D195" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B196">
         <v>2</v>
@@ -5046,12 +5043,12 @@
         <v>5</v>
       </c>
       <c r="D196" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B197">
         <v>2</v>
@@ -5060,12 +5057,12 @@
         <v>7</v>
       </c>
       <c r="D197" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B198">
         <v>3</v>
@@ -5074,12 +5071,12 @@
         <v>5</v>
       </c>
       <c r="D198" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B199">
         <v>3</v>
@@ -5088,12 +5085,12 @@
         <v>7</v>
       </c>
       <c r="D199" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B200">
         <v>4</v>
@@ -5102,12 +5099,12 @@
         <v>5</v>
       </c>
       <c r="D200" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B201">
         <v>4</v>
@@ -5116,12 +5113,12 @@
         <v>7</v>
       </c>
       <c r="D201" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -5130,12 +5127,12 @@
         <v>5</v>
       </c>
       <c r="D202" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -5144,12 +5141,12 @@
         <v>7</v>
       </c>
       <c r="D203" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B204">
         <v>2</v>
@@ -5158,12 +5155,12 @@
         <v>5</v>
       </c>
       <c r="D204" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B205">
         <v>2</v>
@@ -5172,12 +5169,12 @@
         <v>7</v>
       </c>
       <c r="D205" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B206">
         <v>3</v>
@@ -5186,12 +5183,12 @@
         <v>5</v>
       </c>
       <c r="D206" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B207">
         <v>3</v>
@@ -5200,12 +5197,12 @@
         <v>7</v>
       </c>
       <c r="D207" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B208">
         <v>4</v>
@@ -5214,12 +5211,12 @@
         <v>5</v>
       </c>
       <c r="D208" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B209">
         <v>4</v>
@@ -5228,12 +5225,12 @@
         <v>7</v>
       </c>
       <c r="D209" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -5242,12 +5239,12 @@
         <v>5</v>
       </c>
       <c r="D210" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -5256,12 +5253,12 @@
         <v>7</v>
       </c>
       <c r="D211" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B212">
         <v>2</v>
@@ -5270,12 +5267,12 @@
         <v>5</v>
       </c>
       <c r="D212" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B213">
         <v>2</v>
@@ -5284,12 +5281,12 @@
         <v>7</v>
       </c>
       <c r="D213" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B214">
         <v>3</v>
@@ -5298,12 +5295,12 @@
         <v>5</v>
       </c>
       <c r="D214" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B215">
         <v>3</v>
@@ -5312,12 +5309,12 @@
         <v>7</v>
       </c>
       <c r="D215" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B216">
         <v>4</v>
@@ -5326,12 +5323,12 @@
         <v>5</v>
       </c>
       <c r="D216" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B217">
         <v>4</v>
@@ -5340,12 +5337,12 @@
         <v>7</v>
       </c>
       <c r="D217" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -5354,12 +5351,12 @@
         <v>5</v>
       </c>
       <c r="D218" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -5368,12 +5365,12 @@
         <v>7</v>
       </c>
       <c r="D219" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B220">
         <v>2</v>
@@ -5382,12 +5379,12 @@
         <v>5</v>
       </c>
       <c r="D220" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B221">
         <v>2</v>
@@ -5396,12 +5393,12 @@
         <v>7</v>
       </c>
       <c r="D221" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B222">
         <v>3</v>
@@ -5410,12 +5407,12 @@
         <v>5</v>
       </c>
       <c r="D222" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B223">
         <v>3</v>
@@ -5424,12 +5421,12 @@
         <v>7</v>
       </c>
       <c r="D223" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B224">
         <v>4</v>
@@ -5438,12 +5435,12 @@
         <v>5</v>
       </c>
       <c r="D224" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B225">
         <v>4</v>
@@ -5452,12 +5449,12 @@
         <v>7</v>
       </c>
       <c r="D225" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -5466,12 +5463,12 @@
         <v>5</v>
       </c>
       <c r="D226" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -5480,12 +5477,12 @@
         <v>7</v>
       </c>
       <c r="D227" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B228">
         <v>2</v>
@@ -5494,12 +5491,12 @@
         <v>5</v>
       </c>
       <c r="D228" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B229">
         <v>2</v>
@@ -5508,12 +5505,12 @@
         <v>7</v>
       </c>
       <c r="D229" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B230">
         <v>3</v>
@@ -5522,12 +5519,12 @@
         <v>5</v>
       </c>
       <c r="D230" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B231">
         <v>3</v>
@@ -5536,12 +5533,12 @@
         <v>7</v>
       </c>
       <c r="D231" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B232">
         <v>4</v>
@@ -5550,12 +5547,12 @@
         <v>5</v>
       </c>
       <c r="D232" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B233">
         <v>4</v>
@@ -5564,12 +5561,12 @@
         <v>7</v>
       </c>
       <c r="D233" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -5578,12 +5575,12 @@
         <v>5</v>
       </c>
       <c r="D234" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -5592,12 +5589,12 @@
         <v>7</v>
       </c>
       <c r="D235" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B236">
         <v>2</v>
@@ -5606,12 +5603,12 @@
         <v>5</v>
       </c>
       <c r="D236" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B237">
         <v>2</v>
@@ -5620,12 +5617,12 @@
         <v>7</v>
       </c>
       <c r="D237" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B238">
         <v>3</v>
@@ -5634,12 +5631,12 @@
         <v>5</v>
       </c>
       <c r="D238" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B239">
         <v>3</v>
@@ -5648,12 +5645,12 @@
         <v>7</v>
       </c>
       <c r="D239" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B240">
         <v>4</v>
@@ -5662,12 +5659,12 @@
         <v>5</v>
       </c>
       <c r="D240" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B241">
         <v>4</v>
@@ -5676,12 +5673,12 @@
         <v>7</v>
       </c>
       <c r="D241" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -5690,12 +5687,12 @@
         <v>5</v>
       </c>
       <c r="D242" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -5704,12 +5701,12 @@
         <v>7</v>
       </c>
       <c r="D243" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B244">
         <v>2</v>
@@ -5718,12 +5715,12 @@
         <v>5</v>
       </c>
       <c r="D244" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B245">
         <v>2</v>
@@ -5732,12 +5729,12 @@
         <v>7</v>
       </c>
       <c r="D245" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B246">
         <v>3</v>
@@ -5746,12 +5743,12 @@
         <v>5</v>
       </c>
       <c r="D246" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B247">
         <v>3</v>
@@ -5760,12 +5757,12 @@
         <v>7</v>
       </c>
       <c r="D247" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B248">
         <v>4</v>
@@ -5774,12 +5771,12 @@
         <v>5</v>
       </c>
       <c r="D248" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B249">
         <v>4</v>
@@ -5788,12 +5785,12 @@
         <v>7</v>
       </c>
       <c r="D249" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B250">
         <v>1</v>
@@ -5802,12 +5799,12 @@
         <v>5</v>
       </c>
       <c r="D250" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B251">
         <v>1</v>
@@ -5816,12 +5813,12 @@
         <v>7</v>
       </c>
       <c r="D251" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B252">
         <v>2</v>
@@ -5830,12 +5827,12 @@
         <v>5</v>
       </c>
       <c r="D252" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B253">
         <v>2</v>
@@ -5844,12 +5841,12 @@
         <v>7</v>
       </c>
       <c r="D253" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B254">
         <v>3</v>
@@ -5858,12 +5855,12 @@
         <v>5</v>
       </c>
       <c r="D254" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B255">
         <v>3</v>
@@ -5872,12 +5869,12 @@
         <v>7</v>
       </c>
       <c r="D255" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B256">
         <v>4</v>
@@ -5886,12 +5883,12 @@
         <v>5</v>
       </c>
       <c r="D256" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B257">
         <v>4</v>
@@ -5900,12 +5897,12 @@
         <v>7</v>
       </c>
       <c r="D257" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -5914,12 +5911,12 @@
         <v>5</v>
       </c>
       <c r="D258" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -5928,12 +5925,12 @@
         <v>7</v>
       </c>
       <c r="D259" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B260">
         <v>2</v>
@@ -5942,12 +5939,12 @@
         <v>5</v>
       </c>
       <c r="D260" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B261">
         <v>2</v>
@@ -5956,12 +5953,12 @@
         <v>7</v>
       </c>
       <c r="D261" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B262">
         <v>3</v>
@@ -5970,12 +5967,12 @@
         <v>5</v>
       </c>
       <c r="D262" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B263">
         <v>3</v>
@@ -5984,12 +5981,12 @@
         <v>7</v>
       </c>
       <c r="D263" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B264">
         <v>4</v>
@@ -5998,12 +5995,12 @@
         <v>5</v>
       </c>
       <c r="D264" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B265">
         <v>4</v>
@@ -6012,12 +6009,12 @@
         <v>7</v>
       </c>
       <c r="D265" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B266">
         <v>1</v>
@@ -6026,12 +6023,12 @@
         <v>5</v>
       </c>
       <c r="D266" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -6040,12 +6037,12 @@
         <v>7</v>
       </c>
       <c r="D267" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B268">
         <v>2</v>
@@ -6054,12 +6051,12 @@
         <v>5</v>
       </c>
       <c r="D268" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B269">
         <v>2</v>
@@ -6068,12 +6065,12 @@
         <v>7</v>
       </c>
       <c r="D269" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B270">
         <v>3</v>
@@ -6082,12 +6079,12 @@
         <v>5</v>
       </c>
       <c r="D270" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B271">
         <v>3</v>
@@ -6096,12 +6093,12 @@
         <v>7</v>
       </c>
       <c r="D271" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B272">
         <v>4</v>
@@ -6110,12 +6107,12 @@
         <v>5</v>
       </c>
       <c r="D272" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B273">
         <v>4</v>
@@ -6124,12 +6121,12 @@
         <v>7</v>
       </c>
       <c r="D273" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -6138,12 +6135,12 @@
         <v>5</v>
       </c>
       <c r="D274" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B275">
         <v>1</v>
@@ -6152,12 +6149,12 @@
         <v>7</v>
       </c>
       <c r="D275" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B276">
         <v>2</v>
@@ -6166,12 +6163,12 @@
         <v>5</v>
       </c>
       <c r="D276" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B277">
         <v>2</v>
@@ -6180,12 +6177,12 @@
         <v>7</v>
       </c>
       <c r="D277" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B278">
         <v>3</v>
@@ -6194,12 +6191,12 @@
         <v>5</v>
       </c>
       <c r="D278" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B279">
         <v>3</v>
@@ -6208,12 +6205,12 @@
         <v>7</v>
       </c>
       <c r="D279" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B280">
         <v>4</v>
@@ -6222,12 +6219,12 @@
         <v>5</v>
       </c>
       <c r="D280" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B281">
         <v>4</v>
@@ -6236,12 +6233,12 @@
         <v>7</v>
       </c>
       <c r="D281" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B282">
         <v>1</v>
@@ -6250,12 +6247,12 @@
         <v>5</v>
       </c>
       <c r="D282" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B283">
         <v>1</v>
@@ -6264,12 +6261,12 @@
         <v>7</v>
       </c>
       <c r="D283" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B284">
         <v>2</v>
@@ -6278,12 +6275,12 @@
         <v>5</v>
       </c>
       <c r="D284" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B285">
         <v>2</v>
@@ -6292,12 +6289,12 @@
         <v>7</v>
       </c>
       <c r="D285" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B286">
         <v>3</v>
@@ -6306,12 +6303,12 @@
         <v>5</v>
       </c>
       <c r="D286" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B287">
         <v>3</v>
@@ -6320,12 +6317,12 @@
         <v>7</v>
       </c>
       <c r="D287" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B288">
         <v>4</v>
@@ -6334,12 +6331,12 @@
         <v>5</v>
       </c>
       <c r="D288" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B289">
         <v>4</v>
@@ -6348,12 +6345,12 @@
         <v>7</v>
       </c>
       <c r="D289" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -6362,12 +6359,12 @@
         <v>5</v>
       </c>
       <c r="D290" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B291">
         <v>1</v>
@@ -6376,12 +6373,12 @@
         <v>7</v>
       </c>
       <c r="D291" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B292">
         <v>2</v>
@@ -6390,12 +6387,12 @@
         <v>5</v>
       </c>
       <c r="D292" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B293">
         <v>2</v>
@@ -6404,12 +6401,12 @@
         <v>7</v>
       </c>
       <c r="D293" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B294">
         <v>3</v>
@@ -6418,12 +6415,12 @@
         <v>5</v>
       </c>
       <c r="D294" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B295">
         <v>3</v>
@@ -6432,12 +6429,12 @@
         <v>7</v>
       </c>
       <c r="D295" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B296">
         <v>4</v>
@@ -6446,12 +6443,12 @@
         <v>5</v>
       </c>
       <c r="D296" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B297">
         <v>4</v>
@@ -6460,12 +6457,12 @@
         <v>7</v>
       </c>
       <c r="D297" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B298">
         <v>1</v>
@@ -6474,12 +6471,12 @@
         <v>5</v>
       </c>
       <c r="D298" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B299">
         <v>1</v>
@@ -6488,12 +6485,12 @@
         <v>7</v>
       </c>
       <c r="D299" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B300">
         <v>2</v>
@@ -6502,12 +6499,12 @@
         <v>5</v>
       </c>
       <c r="D300" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B301">
         <v>2</v>
@@ -6516,12 +6513,12 @@
         <v>7</v>
       </c>
       <c r="D301" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B302">
         <v>3</v>
@@ -6530,12 +6527,12 @@
         <v>5</v>
       </c>
       <c r="D302" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B303">
         <v>3</v>
@@ -6544,12 +6541,12 @@
         <v>7</v>
       </c>
       <c r="D303" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B304">
         <v>4</v>
@@ -6558,12 +6555,12 @@
         <v>5</v>
       </c>
       <c r="D304" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B305">
         <v>4</v>
@@ -6572,12 +6569,12 @@
         <v>7</v>
       </c>
       <c r="D305" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B306">
         <v>1</v>
@@ -6586,12 +6583,12 @@
         <v>5</v>
       </c>
       <c r="D306" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B307">
         <v>1</v>
@@ -6600,12 +6597,12 @@
         <v>7</v>
       </c>
       <c r="D307" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B308">
         <v>2</v>
@@ -6614,12 +6611,12 @@
         <v>5</v>
       </c>
       <c r="D308" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B309">
         <v>2</v>
@@ -6628,12 +6625,12 @@
         <v>7</v>
       </c>
       <c r="D309" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B310">
         <v>3</v>
@@ -6642,12 +6639,12 @@
         <v>5</v>
       </c>
       <c r="D310" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B311">
         <v>3</v>
@@ -6656,12 +6653,12 @@
         <v>7</v>
       </c>
       <c r="D311" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B312">
         <v>4</v>
@@ -6670,12 +6667,12 @@
         <v>5</v>
       </c>
       <c r="D312" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B313">
         <v>4</v>
@@ -6684,12 +6681,12 @@
         <v>7</v>
       </c>
       <c r="D313" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B314">
         <v>1</v>
@@ -6698,12 +6695,12 @@
         <v>5</v>
       </c>
       <c r="D314" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B315">
         <v>1</v>
@@ -6712,12 +6709,12 @@
         <v>7</v>
       </c>
       <c r="D315" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B316">
         <v>2</v>
@@ -6726,12 +6723,12 @@
         <v>5</v>
       </c>
       <c r="D316" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B317">
         <v>2</v>
@@ -6740,12 +6737,12 @@
         <v>7</v>
       </c>
       <c r="D317" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B318">
         <v>3</v>
@@ -6754,12 +6751,12 @@
         <v>5</v>
       </c>
       <c r="D318" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B319">
         <v>3</v>
@@ -6768,12 +6765,12 @@
         <v>7</v>
       </c>
       <c r="D319" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B320">
         <v>4</v>
@@ -6782,12 +6779,12 @@
         <v>5</v>
       </c>
       <c r="D320" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B321">
         <v>4</v>
@@ -6796,12 +6793,12 @@
         <v>7</v>
       </c>
       <c r="D321" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B322">
         <v>1</v>
@@ -6810,12 +6807,12 @@
         <v>5</v>
       </c>
       <c r="D322" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B323">
         <v>1</v>
@@ -6824,12 +6821,12 @@
         <v>7</v>
       </c>
       <c r="D323" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B324">
         <v>2</v>
@@ -6838,12 +6835,12 @@
         <v>5</v>
       </c>
       <c r="D324" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B325">
         <v>2</v>
@@ -6852,12 +6849,12 @@
         <v>7</v>
       </c>
       <c r="D325" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B326">
         <v>3</v>
@@ -6866,12 +6863,12 @@
         <v>5</v>
       </c>
       <c r="D326" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B327">
         <v>3</v>
@@ -6880,12 +6877,12 @@
         <v>7</v>
       </c>
       <c r="D327" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B328">
         <v>4</v>
@@ -6894,12 +6891,12 @@
         <v>5</v>
       </c>
       <c r="D328" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B329">
         <v>4</v>
@@ -6908,119 +6905,7 @@
         <v>7</v>
       </c>
       <c r="D329" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4">
-      <c r="A330" t="s">
-        <v>367</v>
-      </c>
-      <c r="B330">
-        <v>1</v>
-      </c>
-      <c r="C330" t="s">
-        <v>5</v>
-      </c>
-      <c r="D330" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4">
-      <c r="A331" t="s">
-        <v>367</v>
-      </c>
-      <c r="B331">
-        <v>1</v>
-      </c>
-      <c r="C331" t="s">
-        <v>7</v>
-      </c>
-      <c r="D331" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4">
-      <c r="A332" t="s">
-        <v>367</v>
-      </c>
-      <c r="B332">
-        <v>2</v>
-      </c>
-      <c r="C332" t="s">
-        <v>5</v>
-      </c>
-      <c r="D332" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4">
-      <c r="A333" t="s">
-        <v>367</v>
-      </c>
-      <c r="B333">
-        <v>2</v>
-      </c>
-      <c r="C333" t="s">
-        <v>7</v>
-      </c>
-      <c r="D333" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4">
-      <c r="A334" t="s">
-        <v>367</v>
-      </c>
-      <c r="B334">
-        <v>3</v>
-      </c>
-      <c r="C334" t="s">
-        <v>5</v>
-      </c>
-      <c r="D334" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4">
-      <c r="A335" t="s">
-        <v>367</v>
-      </c>
-      <c r="B335">
-        <v>3</v>
-      </c>
-      <c r="C335" t="s">
-        <v>7</v>
-      </c>
-      <c r="D335" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4">
-      <c r="A336" t="s">
-        <v>367</v>
-      </c>
-      <c r="B336">
-        <v>4</v>
-      </c>
-      <c r="C336" t="s">
-        <v>5</v>
-      </c>
-      <c r="D336" t="s">
         <v>374</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4">
-      <c r="A337" t="s">
-        <v>367</v>
-      </c>
-      <c r="B337">
-        <v>4</v>
-      </c>
-      <c r="C337" t="s">
-        <v>7</v>
-      </c>
-      <c r="D337" t="s">
-        <v>375</v>
       </c>
     </row>
   </sheetData>
